--- a/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_oil_gas_production_and_exploration.xlsx
@@ -1151,7 +1151,7 @@
         <v>112.4</v>
       </c>
       <c r="L2">
-        <v>8.70645868651636</v>
+        <v>8.70645868651633</v>
       </c>
       <c r="M2">
         <v>46.4</v>
@@ -1191,13 +1191,13 @@
         <v>0.193811485631725</v>
       </c>
       <c r="X2">
-        <v>2.31177709284236</v>
+        <v>2.31177709284237</v>
       </c>
       <c r="Y2">
         <v>1.19023852397659</v>
       </c>
       <c r="Z2">
-        <v>18.2219185142168</v>
+        <v>18.2219185142169</v>
       </c>
       <c r="AA2">
         <v>35.7</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1654064470587434</v>
+        <v>0.1650228067565578</v>
       </c>
       <c r="C2">
-        <v>148.2394579656263</v>
+        <v>146.7873405206379</v>
       </c>
       <c r="D2">
-        <v>46.53945796562627</v>
+        <v>46.5683405206379</v>
       </c>
       <c r="E2">
-        <v>-35.7</v>
+        <v>-34.219</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.481</v>
       </c>
       <c r="G2">
         <v>101.7</v>
@@ -1451,28 +1451,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.07449430000000001</v>
       </c>
       <c r="N2">
-        <v>35.64285714285715</v>
+        <v>35.56836284285716</v>
       </c>
       <c r="O2">
-        <v>8.991986661451678</v>
+        <v>8.973193225525108</v>
       </c>
       <c r="P2">
-        <v>26.65087048140548</v>
+        <v>26.59516961733205</v>
       </c>
       <c r="Q2">
-        <v>63.15087048140548</v>
+        <v>63.09516961733205</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1654064470587434</v>
+        <v>0.1663098017076422</v>
       </c>
       <c r="T2">
-        <v>0.9618186075065634</v>
+        <v>0.9690829593191519</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>478.4642199853834</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1650228067565578</v>
+        <v>0.1646391664543724</v>
       </c>
       <c r="C3">
-        <v>146.7873405206379</v>
+        <v>145.3352589471466</v>
       </c>
       <c r="D3">
-        <v>46.5683405206379</v>
+        <v>46.59725894714655</v>
       </c>
       <c r="E3">
-        <v>-34.219</v>
+        <v>-32.738</v>
       </c>
       <c r="F3">
-        <v>1.481</v>
+        <v>2.962000000000001</v>
       </c>
       <c r="G3">
         <v>101.7</v>
@@ -1533,28 +1533,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M3">
-        <v>0.07449430000000001</v>
+        <v>0.1489886</v>
       </c>
       <c r="N3">
-        <v>35.56836284285716</v>
+        <v>35.49386854285715</v>
       </c>
       <c r="O3">
-        <v>8.973193225525108</v>
+        <v>8.954399789598536</v>
       </c>
       <c r="P3">
-        <v>26.59516961733205</v>
+        <v>26.53946875325861</v>
       </c>
       <c r="Q3">
-        <v>63.09516961733205</v>
+        <v>63.03946875325862</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1663098017076422</v>
+        <v>0.1672315921657022</v>
       </c>
       <c r="T3">
-        <v>0.9690829593191519</v>
+        <v>0.9764955632095484</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>478.4642199853834</v>
+        <v>239.2321099926917</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1646391664543724</v>
+        <v>0.1642555261521869</v>
       </c>
       <c r="C4">
-        <v>145.3352589471466</v>
+        <v>143.8832133120212</v>
       </c>
       <c r="D4">
-        <v>46.59725894714655</v>
+        <v>46.62621331202119</v>
       </c>
       <c r="E4">
-        <v>-32.738</v>
+        <v>-31.257</v>
       </c>
       <c r="F4">
-        <v>2.962000000000001</v>
+        <v>4.443000000000001</v>
       </c>
       <c r="G4">
         <v>101.7</v>
@@ -1615,28 +1615,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M4">
-        <v>0.1489886</v>
+        <v>0.2234829</v>
       </c>
       <c r="N4">
-        <v>35.49386854285715</v>
+        <v>35.41937424285715</v>
       </c>
       <c r="O4">
-        <v>8.954399789598536</v>
+        <v>8.935606353671966</v>
       </c>
       <c r="P4">
-        <v>26.53946875325861</v>
+        <v>26.48376788918519</v>
       </c>
       <c r="Q4">
-        <v>63.03946875325862</v>
+        <v>62.98376788918519</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1672315921657022</v>
+        <v>0.1681723886125882</v>
       </c>
       <c r="T4">
-        <v>0.9764955632095484</v>
+        <v>0.9840610042935614</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>239.2321099926917</v>
+        <v>159.4880733284612</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1642555261521869</v>
+        <v>0.1638718858500014</v>
       </c>
       <c r="C5">
-        <v>143.8832133120212</v>
+        <v>142.431203682297</v>
       </c>
       <c r="D5">
-        <v>46.62621331202119</v>
+        <v>46.65520368229704</v>
       </c>
       <c r="E5">
-        <v>-31.257</v>
+        <v>-29.776</v>
       </c>
       <c r="F5">
-        <v>4.443000000000001</v>
+        <v>5.924000000000001</v>
       </c>
       <c r="G5">
         <v>101.7</v>
@@ -1697,28 +1697,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M5">
-        <v>0.2234829</v>
+        <v>0.2979772000000001</v>
       </c>
       <c r="N5">
-        <v>35.41937424285715</v>
+        <v>35.34487994285715</v>
       </c>
       <c r="O5">
-        <v>8.935606353671966</v>
+        <v>8.916812917745396</v>
       </c>
       <c r="P5">
-        <v>26.48376788918519</v>
+        <v>26.42806702511176</v>
       </c>
       <c r="Q5">
-        <v>62.98376788918519</v>
+        <v>62.92806702511176</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1681723886125882</v>
+        <v>0.169132784985451</v>
       </c>
       <c r="T5">
-        <v>0.9840610042935614</v>
+        <v>0.9917840587334911</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>159.4880733284612</v>
+        <v>119.6160549963459</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1638718858500014</v>
+        <v>0.1634882455478159</v>
       </c>
       <c r="C6">
-        <v>142.431203682297</v>
+        <v>140.9792301251762</v>
       </c>
       <c r="D6">
-        <v>46.65520368229704</v>
+        <v>46.68423012517619</v>
       </c>
       <c r="E6">
-        <v>-29.776</v>
+        <v>-28.295</v>
       </c>
       <c r="F6">
-        <v>5.924000000000001</v>
+        <v>7.405000000000001</v>
       </c>
       <c r="G6">
         <v>101.7</v>
@@ -1779,28 +1779,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M6">
-        <v>0.2979772000000001</v>
+        <v>0.3724715</v>
       </c>
       <c r="N6">
-        <v>35.34487994285715</v>
+        <v>35.27038564285715</v>
       </c>
       <c r="O6">
-        <v>8.916812917745396</v>
+        <v>8.898019481818826</v>
       </c>
       <c r="P6">
-        <v>26.42806702511176</v>
+        <v>26.37236616103832</v>
       </c>
       <c r="Q6">
-        <v>62.92806702511176</v>
+        <v>62.87236616103832</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.169132784985451</v>
+        <v>0.1701134002293215</v>
       </c>
       <c r="T6">
-        <v>0.9917840587334911</v>
+        <v>0.9996697037932089</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>119.6160549963459</v>
+        <v>95.69284399707668</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1634882455478159</v>
+        <v>0.1631046052456304</v>
       </c>
       <c r="C7">
-        <v>140.9792301251762</v>
+        <v>139.527292708028</v>
       </c>
       <c r="D7">
-        <v>46.68423012517619</v>
+        <v>46.71329270802803</v>
       </c>
       <c r="E7">
-        <v>-28.295</v>
+        <v>-26.814</v>
       </c>
       <c r="F7">
-        <v>7.405000000000001</v>
+        <v>8.886000000000003</v>
       </c>
       <c r="G7">
         <v>101.7</v>
@@ -1861,28 +1861,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M7">
-        <v>0.3724715</v>
+        <v>0.4469658000000001</v>
       </c>
       <c r="N7">
-        <v>35.27038564285715</v>
+        <v>35.19589134285715</v>
       </c>
       <c r="O7">
-        <v>8.898019481818826</v>
+        <v>8.879226045892256</v>
       </c>
       <c r="P7">
-        <v>26.37236616103832</v>
+        <v>26.3166652969649</v>
       </c>
       <c r="Q7">
-        <v>62.87236616103832</v>
+        <v>62.8166652969649</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1701134002293215</v>
+        <v>0.1711148796273168</v>
       </c>
       <c r="T7">
-        <v>0.9996697037932089</v>
+        <v>1.007723128535048</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>95.69284399707668</v>
+        <v>79.74403666423055</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1631046052456304</v>
+        <v>0.1627209649434449</v>
       </c>
       <c r="C8">
-        <v>139.527292708028</v>
+        <v>138.0753914983898</v>
       </c>
       <c r="D8">
-        <v>46.71329270802803</v>
+        <v>46.74239149838984</v>
       </c>
       <c r="E8">
-        <v>-26.814</v>
+        <v>-25.333</v>
       </c>
       <c r="F8">
-        <v>8.886000000000001</v>
+        <v>10.367</v>
       </c>
       <c r="G8">
         <v>101.7</v>
@@ -1943,28 +1943,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M8">
-        <v>0.4469658</v>
+        <v>0.5214601</v>
       </c>
       <c r="N8">
-        <v>35.19589134285715</v>
+        <v>35.12139704285715</v>
       </c>
       <c r="O8">
-        <v>8.879226045892256</v>
+        <v>8.860432609965686</v>
       </c>
       <c r="P8">
-        <v>26.3166652969649</v>
+        <v>26.26096443289147</v>
       </c>
       <c r="Q8">
-        <v>62.8166652969649</v>
+        <v>62.76096443289147</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1711148796273168</v>
+        <v>0.1721378962166669</v>
       </c>
       <c r="T8">
-        <v>1.007723128535048</v>
+        <v>1.01594974520682</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>79.74403666423058</v>
+        <v>68.35203142648336</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1627209649434448</v>
+        <v>0.1623373246412594</v>
       </c>
       <c r="C9">
-        <v>138.0753914983898</v>
+        <v>136.6235265639673</v>
       </c>
       <c r="D9">
-        <v>46.74239149838984</v>
+        <v>46.77152656396728</v>
       </c>
       <c r="E9">
-        <v>-25.333</v>
+        <v>-23.852</v>
       </c>
       <c r="F9">
-        <v>10.367</v>
+        <v>11.848</v>
       </c>
       <c r="G9">
         <v>101.7</v>
@@ -2025,28 +2025,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M9">
-        <v>0.5214601000000001</v>
+        <v>0.5959544000000001</v>
       </c>
       <c r="N9">
-        <v>35.12139704285715</v>
+        <v>35.04690274285716</v>
       </c>
       <c r="O9">
-        <v>8.860432609965686</v>
+        <v>8.841639174039116</v>
       </c>
       <c r="P9">
-        <v>26.26096443289147</v>
+        <v>26.20526356881804</v>
       </c>
       <c r="Q9">
-        <v>62.76096443289147</v>
+        <v>62.70526356881804</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1721378962166669</v>
+        <v>0.1731831522970898</v>
       </c>
       <c r="T9">
-        <v>1.01594974520682</v>
+        <v>1.024355201371456</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>68.35203142648335</v>
+        <v>59.80802749817293</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1623373246412594</v>
+        <v>0.1619536843390739</v>
       </c>
       <c r="C10">
-        <v>136.6235265639673</v>
+        <v>135.1716979726349</v>
       </c>
       <c r="D10">
-        <v>46.77152656396728</v>
+        <v>46.80069797263494</v>
       </c>
       <c r="E10">
-        <v>-23.852</v>
+        <v>-22.371</v>
       </c>
       <c r="F10">
-        <v>11.848</v>
+        <v>13.329</v>
       </c>
       <c r="G10">
         <v>101.7</v>
@@ -2107,28 +2107,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M10">
-        <v>0.5959544000000001</v>
+        <v>0.6704487000000001</v>
       </c>
       <c r="N10">
-        <v>35.04690274285716</v>
+        <v>34.97240844285715</v>
       </c>
       <c r="O10">
-        <v>8.841639174039116</v>
+        <v>8.822845738112546</v>
       </c>
       <c r="P10">
-        <v>26.20526356881804</v>
+        <v>26.1495627047446</v>
       </c>
       <c r="Q10">
-        <v>62.70526356881804</v>
+        <v>62.6495627047446</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1731831522970898</v>
+        <v>0.1742513810386209</v>
       </c>
       <c r="T10">
-        <v>1.024355201371456</v>
+        <v>1.032945392836413</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>59.80802749817293</v>
+        <v>53.16269110948704</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1619536843390739</v>
+        <v>0.1615700440368884</v>
       </c>
       <c r="C11">
-        <v>135.1716979726349</v>
+        <v>133.7199057924368</v>
       </c>
       <c r="D11">
-        <v>46.80069797263494</v>
+        <v>46.82990579243681</v>
       </c>
       <c r="E11">
-        <v>-22.371</v>
+        <v>-20.89</v>
       </c>
       <c r="F11">
-        <v>13.329</v>
+        <v>14.81</v>
       </c>
       <c r="G11">
         <v>101.7</v>
@@ -2189,28 +2189,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M11">
-        <v>0.6704487000000001</v>
+        <v>0.744943</v>
       </c>
       <c r="N11">
-        <v>34.97240844285715</v>
+        <v>34.89791414285715</v>
       </c>
       <c r="O11">
-        <v>8.822845738112546</v>
+        <v>8.804052302185976</v>
       </c>
       <c r="P11">
-        <v>26.1495627047446</v>
+        <v>26.09386184067118</v>
       </c>
       <c r="Q11">
-        <v>62.6495627047446</v>
+        <v>62.59386184067118</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1742513810386209</v>
+        <v>0.1753433481966305</v>
       </c>
       <c r="T11">
-        <v>1.032945392836413</v>
+        <v>1.041726477445037</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>53.16269110948704</v>
+        <v>47.84642199853835</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1615700440368884</v>
+        <v>0.1611864037347029</v>
       </c>
       <c r="C12">
-        <v>133.7199057924368</v>
+        <v>132.2681500915869</v>
       </c>
       <c r="D12">
-        <v>46.82990579243681</v>
+        <v>46.85915009158688</v>
       </c>
       <c r="E12">
-        <v>-20.89</v>
+        <v>-19.409</v>
       </c>
       <c r="F12">
-        <v>14.81</v>
+        <v>16.291</v>
       </c>
       <c r="G12">
         <v>101.7</v>
@@ -2271,28 +2271,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M12">
-        <v>0.744943</v>
+        <v>0.8194373000000001</v>
       </c>
       <c r="N12">
-        <v>34.89791414285715</v>
+        <v>34.82341984285716</v>
       </c>
       <c r="O12">
-        <v>8.804052302185976</v>
+        <v>8.785258866259406</v>
       </c>
       <c r="P12">
-        <v>26.09386184067118</v>
+        <v>26.03816097659775</v>
       </c>
       <c r="Q12">
-        <v>62.59386184067118</v>
+        <v>62.53816097659775</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1753433481966305</v>
+        <v>0.1764598539424605</v>
       </c>
       <c r="T12">
-        <v>1.041726477445037</v>
+        <v>1.050704889797675</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>47.84642199853835</v>
+        <v>43.4967472713985</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1611864037347029</v>
+        <v>0.1608027634325174</v>
       </c>
       <c r="C13">
-        <v>132.2681500915869</v>
+        <v>130.8164309384697</v>
       </c>
       <c r="D13">
-        <v>46.85915009158688</v>
+        <v>46.88843093846965</v>
       </c>
       <c r="E13">
-        <v>-19.409</v>
+        <v>-17.928</v>
       </c>
       <c r="F13">
-        <v>16.291</v>
+        <v>17.772</v>
       </c>
       <c r="G13">
         <v>101.7</v>
@@ -2353,28 +2353,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M13">
-        <v>0.8194373000000001</v>
+        <v>0.8939316</v>
       </c>
       <c r="N13">
-        <v>34.82341984285716</v>
+        <v>34.74892554285715</v>
       </c>
       <c r="O13">
-        <v>8.785258866259406</v>
+        <v>8.766465430332834</v>
       </c>
       <c r="P13">
-        <v>26.03816097659775</v>
+        <v>25.98246011252431</v>
       </c>
       <c r="Q13">
-        <v>62.53816097659775</v>
+        <v>62.48246011252431</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1764598539424605</v>
+        <v>0.1776017348188775</v>
       </c>
       <c r="T13">
-        <v>1.050704889797675</v>
+        <v>1.059887356976508</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>43.4967472713985</v>
+        <v>39.87201833211529</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1608027634325174</v>
+        <v>0.1604191231303319</v>
       </c>
       <c r="C14">
-        <v>130.8164309384697</v>
+        <v>129.3647484016406</v>
       </c>
       <c r="D14">
-        <v>46.88843093846965</v>
+        <v>46.91774840164059</v>
       </c>
       <c r="E14">
-        <v>-17.928</v>
+        <v>-16.447</v>
       </c>
       <c r="F14">
-        <v>17.772</v>
+        <v>19.253</v>
       </c>
       <c r="G14">
         <v>101.7</v>
@@ -2435,28 +2435,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M14">
-        <v>0.8939316</v>
+        <v>0.9684259000000002</v>
       </c>
       <c r="N14">
-        <v>34.74892554285715</v>
+        <v>34.67443124285715</v>
       </c>
       <c r="O14">
-        <v>8.766465430332834</v>
+        <v>8.747671994406264</v>
       </c>
       <c r="P14">
-        <v>25.98246011252431</v>
+        <v>25.92675924845089</v>
       </c>
       <c r="Q14">
-        <v>62.48246011252431</v>
+        <v>62.42675924845089</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1776017348188775</v>
+        <v>0.1787698658303846</v>
       </c>
       <c r="T14">
-        <v>1.059887356976508</v>
+        <v>1.069280915354855</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>39.87201833211529</v>
+        <v>36.80493999887565</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1604191231303319</v>
+        <v>0.1600354828281464</v>
       </c>
       <c r="C15">
-        <v>129.3647484016406</v>
+        <v>127.9131025498268</v>
       </c>
       <c r="D15">
-        <v>46.91774840164059</v>
+        <v>46.94710254982681</v>
       </c>
       <c r="E15">
-        <v>-16.447</v>
+        <v>-14.966</v>
       </c>
       <c r="F15">
-        <v>19.253</v>
+        <v>20.73400000000001</v>
       </c>
       <c r="G15">
         <v>101.7</v>
@@ -2517,28 +2517,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M15">
-        <v>0.9684259000000002</v>
+        <v>1.0429202</v>
       </c>
       <c r="N15">
-        <v>34.67443124285715</v>
+        <v>34.59993694285716</v>
       </c>
       <c r="O15">
-        <v>8.747671994406264</v>
+        <v>8.728878558479696</v>
       </c>
       <c r="P15">
-        <v>25.92675924845089</v>
+        <v>25.87105838437746</v>
       </c>
       <c r="Q15">
-        <v>62.42675924845089</v>
+        <v>62.37105838437746</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1787698658303846</v>
+        <v>0.1799651626793687</v>
       </c>
       <c r="T15">
-        <v>1.069280915354855</v>
+        <v>1.078892928579211</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>36.80493999887565</v>
+        <v>34.17601571324168</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1600354828281464</v>
+        <v>0.1596518425259609</v>
       </c>
       <c r="C16">
-        <v>127.9131025498268</v>
+        <v>126.4614934519275</v>
       </c>
       <c r="D16">
-        <v>46.94710254982681</v>
+        <v>46.9764934519275</v>
       </c>
       <c r="E16">
-        <v>-14.966</v>
+        <v>-13.485</v>
       </c>
       <c r="F16">
-        <v>20.73400000000001</v>
+        <v>22.21500000000001</v>
       </c>
       <c r="G16">
         <v>101.7</v>
@@ -2599,28 +2599,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M16">
-        <v>1.0429202</v>
+        <v>1.1174145</v>
       </c>
       <c r="N16">
-        <v>34.59993694285716</v>
+        <v>34.52544264285715</v>
       </c>
       <c r="O16">
-        <v>8.728878558479696</v>
+        <v>8.710085122553124</v>
       </c>
       <c r="P16">
-        <v>25.87105838437746</v>
+        <v>25.81535752030403</v>
       </c>
       <c r="Q16">
-        <v>62.37105838437746</v>
+        <v>62.31535752030403</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1799651626793687</v>
+        <v>0.1811885841600935</v>
       </c>
       <c r="T16">
-        <v>1.078892928579211</v>
+        <v>1.08873110682061</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>34.17601571324168</v>
+        <v>31.89761466569222</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1596518425259609</v>
+        <v>0.1592682022237754</v>
       </c>
       <c r="C17">
-        <v>126.4614934519275</v>
+        <v>125.0099211770145</v>
       </c>
       <c r="D17">
-        <v>46.9764934519275</v>
+        <v>47.00592117701446</v>
       </c>
       <c r="E17">
-        <v>-13.485</v>
+        <v>-12.004</v>
       </c>
       <c r="F17">
-        <v>22.215</v>
+        <v>23.69600000000001</v>
       </c>
       <c r="G17">
         <v>101.7</v>
@@ -2681,28 +2681,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M17">
-        <v>1.1174145</v>
+        <v>1.1919088</v>
       </c>
       <c r="N17">
-        <v>34.52544264285715</v>
+        <v>34.45094834285715</v>
       </c>
       <c r="O17">
-        <v>8.710085122553124</v>
+        <v>8.691291686626554</v>
       </c>
       <c r="P17">
-        <v>25.81535752030403</v>
+        <v>25.7596566562306</v>
       </c>
       <c r="Q17">
-        <v>62.31535752030403</v>
+        <v>62.2596566562306</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1811885841600935</v>
+        <v>0.1824411347236927</v>
       </c>
       <c r="T17">
-        <v>1.08873110682061</v>
+        <v>1.098803527401089</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>31.89761466569222</v>
+        <v>29.90401374908646</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1592682022237754</v>
+        <v>0.15888456192159</v>
       </c>
       <c r="C18">
-        <v>125.0099211770145</v>
+        <v>123.5583857943327</v>
       </c>
       <c r="D18">
-        <v>47.00592117701446</v>
+        <v>47.03538579433273</v>
       </c>
       <c r="E18">
-        <v>-12.004</v>
+        <v>-10.523</v>
       </c>
       <c r="F18">
-        <v>23.69600000000001</v>
+        <v>25.17700000000001</v>
       </c>
       <c r="G18">
         <v>101.7</v>
@@ -2763,28 +2763,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M18">
-        <v>1.1919088</v>
+        <v>1.2664031</v>
       </c>
       <c r="N18">
-        <v>34.45094834285715</v>
+        <v>34.37645404285716</v>
       </c>
       <c r="O18">
-        <v>8.691291686626554</v>
+        <v>8.672498250699984</v>
       </c>
       <c r="P18">
-        <v>25.7596566562306</v>
+        <v>25.70395579215717</v>
       </c>
       <c r="Q18">
-        <v>62.2596566562306</v>
+        <v>62.20395579215717</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1824411347236927</v>
+        <v>0.1837238672285835</v>
       </c>
       <c r="T18">
-        <v>1.098803527401089</v>
+        <v>1.109118656911219</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>29.90401374908646</v>
+        <v>28.14495411678726</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.15888456192159</v>
+        <v>0.1585009216194045</v>
       </c>
       <c r="C19">
-        <v>123.5583857943327</v>
+        <v>122.106887373301</v>
       </c>
       <c r="D19">
-        <v>47.03538579433273</v>
+        <v>47.06488737330103</v>
       </c>
       <c r="E19">
-        <v>-10.523</v>
+        <v>-9.041999999999994</v>
       </c>
       <c r="F19">
-        <v>25.17700000000001</v>
+        <v>26.65800000000001</v>
       </c>
       <c r="G19">
         <v>101.7</v>
@@ -2845,28 +2845,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M19">
-        <v>1.2664031</v>
+        <v>1.3408974</v>
       </c>
       <c r="N19">
-        <v>34.37645404285716</v>
+        <v>34.30195974285715</v>
       </c>
       <c r="O19">
-        <v>8.672498250699984</v>
+        <v>8.653704814773414</v>
       </c>
       <c r="P19">
-        <v>25.70395579215717</v>
+        <v>25.64825492808374</v>
       </c>
       <c r="Q19">
-        <v>62.20395579215717</v>
+        <v>62.14825492808374</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1837238672285835</v>
+        <v>0.1850378858921301</v>
       </c>
       <c r="T19">
-        <v>1.109118656911219</v>
+        <v>1.119685374945987</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>28.14495411678726</v>
+        <v>26.58134555474352</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1585009216194045</v>
+        <v>0.158117281317219</v>
       </c>
       <c r="C20">
-        <v>122.106887373301</v>
+        <v>120.6554259835124</v>
       </c>
       <c r="D20">
-        <v>47.06488737330103</v>
+        <v>47.09442598351239</v>
       </c>
       <c r="E20">
-        <v>-9.041999999999998</v>
+        <v>-7.561</v>
       </c>
       <c r="F20">
-        <v>26.658</v>
+        <v>28.139</v>
       </c>
       <c r="G20">
         <v>101.7</v>
@@ -2927,28 +2927,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M20">
-        <v>1.3408974</v>
+        <v>1.4153917</v>
       </c>
       <c r="N20">
-        <v>34.30195974285715</v>
+        <v>34.22746544285715</v>
       </c>
       <c r="O20">
-        <v>8.653704814773414</v>
+        <v>8.634911378846844</v>
       </c>
       <c r="P20">
-        <v>25.64825492808374</v>
+        <v>25.59255406401031</v>
       </c>
       <c r="Q20">
-        <v>62.14825492808374</v>
+        <v>62.09255406401031</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1850378858921301</v>
+        <v>0.1863843494609495</v>
       </c>
       <c r="T20">
-        <v>1.119685374945987</v>
+        <v>1.130512999598897</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>26.58134555474352</v>
+        <v>25.18232736765176</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.158117281317219</v>
+        <v>0.1577336410150335</v>
       </c>
       <c r="C21">
-        <v>120.6554259835124</v>
+        <v>119.2040016947346</v>
       </c>
       <c r="D21">
-        <v>47.09442598351239</v>
+        <v>47.12400169473463</v>
       </c>
       <c r="E21">
-        <v>-7.561</v>
+        <v>-6.079999999999998</v>
       </c>
       <c r="F21">
-        <v>28.139</v>
+        <v>29.62</v>
       </c>
       <c r="G21">
         <v>101.7</v>
@@ -3009,28 +3009,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M21">
-        <v>1.4153917</v>
+        <v>1.489886</v>
       </c>
       <c r="N21">
-        <v>34.22746544285715</v>
+        <v>34.15297114285715</v>
       </c>
       <c r="O21">
-        <v>8.634911378846844</v>
+        <v>8.616117942920274</v>
       </c>
       <c r="P21">
-        <v>25.59255406401031</v>
+        <v>25.53685319993688</v>
       </c>
       <c r="Q21">
-        <v>62.09255406401031</v>
+        <v>62.03685319993688</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1863843494609495</v>
+        <v>0.1877644746189894</v>
       </c>
       <c r="T21">
-        <v>1.130512999598897</v>
+        <v>1.141611314868129</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>25.18232736765176</v>
+        <v>23.92321099926917</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1577336410150335</v>
+        <v>0.157350000712848</v>
       </c>
       <c r="C22">
-        <v>119.2040016947346</v>
+        <v>117.752614576911</v>
       </c>
       <c r="D22">
-        <v>47.12400169473463</v>
+        <v>47.15361457691096</v>
       </c>
       <c r="E22">
-        <v>-6.079999999999998</v>
+        <v>-4.598999999999997</v>
       </c>
       <c r="F22">
-        <v>29.62</v>
+        <v>31.10100000000001</v>
       </c>
       <c r="G22">
         <v>101.7</v>
@@ -3091,28 +3091,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M22">
-        <v>1.489886</v>
+        <v>1.5643803</v>
       </c>
       <c r="N22">
-        <v>34.15297114285715</v>
+        <v>34.07847684285715</v>
       </c>
       <c r="O22">
-        <v>8.616117942920274</v>
+        <v>8.597324506993703</v>
       </c>
       <c r="P22">
-        <v>25.53685319993688</v>
+        <v>25.48115233586345</v>
       </c>
       <c r="Q22">
-        <v>62.03685319993688</v>
+        <v>61.98115233586345</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1877644746189894</v>
+        <v>0.189179539654448</v>
       </c>
       <c r="T22">
-        <v>1.141611314868129</v>
+        <v>1.152990600144177</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>23.92321099926917</v>
+        <v>22.78401047549444</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.157350000712848</v>
+        <v>0.1569663604106625</v>
       </c>
       <c r="C23">
-        <v>117.752614576911</v>
+        <v>116.3012647001605</v>
       </c>
       <c r="D23">
-        <v>47.15361457691096</v>
+        <v>47.18326470016049</v>
       </c>
       <c r="E23">
-        <v>-4.599</v>
+        <v>-3.117999999999995</v>
       </c>
       <c r="F23">
-        <v>31.101</v>
+        <v>32.58200000000001</v>
       </c>
       <c r="G23">
         <v>101.7</v>
@@ -3173,28 +3173,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M23">
-        <v>1.5643803</v>
+        <v>1.6388746</v>
       </c>
       <c r="N23">
-        <v>34.07847684285715</v>
+        <v>34.00398254285715</v>
       </c>
       <c r="O23">
-        <v>8.597324506993703</v>
+        <v>8.578531071067133</v>
       </c>
       <c r="P23">
-        <v>25.48115233586345</v>
+        <v>25.42545147179002</v>
       </c>
       <c r="Q23">
-        <v>61.98115233586345</v>
+        <v>61.92545147179002</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.189179539654448</v>
+        <v>0.1906308884087645</v>
       </c>
       <c r="T23">
-        <v>1.152990600144177</v>
+        <v>1.164661661965765</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>22.78401047549445</v>
+        <v>21.74837363569925</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1569663604106625</v>
+        <v>0.156582720108477</v>
       </c>
       <c r="C24">
-        <v>116.3012647001605</v>
+        <v>114.8499521347788</v>
       </c>
       <c r="D24">
-        <v>47.18326470016049</v>
+        <v>47.21295213477884</v>
       </c>
       <c r="E24">
-        <v>-3.117999999999995</v>
+        <v>-1.636999999999993</v>
       </c>
       <c r="F24">
-        <v>32.58200000000001</v>
+        <v>34.06300000000001</v>
       </c>
       <c r="G24">
         <v>101.7</v>
@@ -3255,28 +3255,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M24">
-        <v>1.6388746</v>
+        <v>1.7133689</v>
       </c>
       <c r="N24">
-        <v>34.00398254285715</v>
+        <v>33.92948824285715</v>
       </c>
       <c r="O24">
-        <v>8.578531071067133</v>
+        <v>8.559737635140564</v>
       </c>
       <c r="P24">
-        <v>25.42545147179002</v>
+        <v>25.36975060771659</v>
       </c>
       <c r="Q24">
-        <v>61.92545147179002</v>
+        <v>61.86975060771659</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1906308884087645</v>
+        <v>0.192119934533323</v>
       </c>
       <c r="T24">
-        <v>1.164661661965765</v>
+        <v>1.176635868250252</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>21.74837363569925</v>
+        <v>20.80279217327754</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.156582720108477</v>
+        <v>0.1561990798062915</v>
       </c>
       <c r="C25">
-        <v>114.8499521347788</v>
+        <v>113.3986769512386</v>
       </c>
       <c r="D25">
-        <v>47.21295213477884</v>
+        <v>47.24267695123863</v>
       </c>
       <c r="E25">
-        <v>-1.636999999999993</v>
+        <v>-0.1559999999999917</v>
       </c>
       <c r="F25">
-        <v>34.06300000000001</v>
+        <v>35.54400000000001</v>
       </c>
       <c r="G25">
         <v>101.7</v>
@@ -3337,28 +3337,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M25">
-        <v>1.7133689</v>
+        <v>1.787863200000001</v>
       </c>
       <c r="N25">
-        <v>33.92948824285715</v>
+        <v>33.85499394285715</v>
       </c>
       <c r="O25">
-        <v>8.559737635140564</v>
+        <v>8.540944199213993</v>
       </c>
       <c r="P25">
-        <v>25.36975060771659</v>
+        <v>25.31404974364316</v>
       </c>
       <c r="Q25">
-        <v>61.86975060771659</v>
+        <v>61.81404974364315</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.192119934533323</v>
+        <v>0.193648166082212</v>
       </c>
       <c r="T25">
-        <v>1.176635868250252</v>
+        <v>1.188925185226436</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>20.80279217327754</v>
+        <v>19.93600916605764</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1561990798062915</v>
+        <v>0.155815439504106</v>
       </c>
       <c r="C26">
-        <v>113.3986769512386</v>
+        <v>111.94743922019</v>
       </c>
       <c r="D26">
-        <v>47.24267695123863</v>
+        <v>47.27243922019005</v>
       </c>
       <c r="E26">
-        <v>-0.1559999999999988</v>
+        <v>1.325000000000003</v>
       </c>
       <c r="F26">
-        <v>35.544</v>
+        <v>37.02500000000001</v>
       </c>
       <c r="G26">
         <v>101.7</v>
@@ -3419,28 +3419,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M26">
-        <v>1.7878632</v>
+        <v>1.8623575</v>
       </c>
       <c r="N26">
-        <v>33.85499394285716</v>
+        <v>33.78049964285715</v>
       </c>
       <c r="O26">
-        <v>8.540944199213994</v>
+        <v>8.522150763287422</v>
       </c>
       <c r="P26">
-        <v>25.31404974364316</v>
+        <v>25.25834887956973</v>
       </c>
       <c r="Q26">
-        <v>61.81404974364316</v>
+        <v>61.75834887956973</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.193648166082212</v>
+        <v>0.1952171504724047</v>
       </c>
       <c r="T26">
-        <v>1.188925185226436</v>
+        <v>1.201542217321984</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>19.93600916605764</v>
+        <v>19.13856879941534</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.155815439504106</v>
+        <v>0.1554317992019205</v>
       </c>
       <c r="C27">
-        <v>111.94743922019</v>
+        <v>110.4962390124615</v>
       </c>
       <c r="D27">
-        <v>47.27243922019005</v>
+        <v>47.30223901246149</v>
       </c>
       <c r="E27">
-        <v>1.325000000000003</v>
+        <v>2.806000000000004</v>
       </c>
       <c r="F27">
-        <v>37.02500000000001</v>
+        <v>38.50600000000001</v>
       </c>
       <c r="G27">
         <v>101.7</v>
@@ -3501,28 +3501,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M27">
-        <v>1.8623575</v>
+        <v>1.9368518</v>
       </c>
       <c r="N27">
-        <v>33.78049964285715</v>
+        <v>33.70600534285715</v>
       </c>
       <c r="O27">
-        <v>8.522150763287422</v>
+        <v>8.503357327360852</v>
       </c>
       <c r="P27">
-        <v>25.25834887956973</v>
+        <v>25.2026480154963</v>
       </c>
       <c r="Q27">
-        <v>61.75834887956973</v>
+        <v>61.7026480154963</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1952171504724047</v>
+        <v>0.1968285398461162</v>
       </c>
       <c r="T27">
-        <v>1.201542217321984</v>
+        <v>1.21450025028498</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>19.13856879941534</v>
+        <v>18.40246999943782</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1554317992019205</v>
+        <v>0.155048158899735</v>
       </c>
       <c r="C28">
-        <v>110.4962390124615</v>
+        <v>109.04507639906</v>
       </c>
       <c r="D28">
-        <v>47.30223901246149</v>
+        <v>47.33207639906002</v>
       </c>
       <c r="E28">
-        <v>2.806000000000004</v>
+        <v>4.287000000000006</v>
       </c>
       <c r="F28">
-        <v>38.50600000000001</v>
+        <v>39.98700000000001</v>
       </c>
       <c r="G28">
         <v>101.7</v>
@@ -3583,28 +3583,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M28">
-        <v>1.9368518</v>
+        <v>2.0113461</v>
       </c>
       <c r="N28">
-        <v>33.70600534285715</v>
+        <v>33.63151104285716</v>
       </c>
       <c r="O28">
-        <v>8.503357327360852</v>
+        <v>8.484563891434284</v>
       </c>
       <c r="P28">
-        <v>25.2026480154963</v>
+        <v>25.14694715142287</v>
       </c>
       <c r="Q28">
-        <v>61.7026480154963</v>
+        <v>61.64694715142287</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1968285398461162</v>
+        <v>0.1984840768739019</v>
       </c>
       <c r="T28">
-        <v>1.21450025028498</v>
+        <v>1.227813297849701</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>18.40246999943782</v>
+        <v>17.72089703649568</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.155048158899735</v>
+        <v>0.1546645185975495</v>
       </c>
       <c r="C29">
-        <v>109.04507639906</v>
+        <v>107.593951451172</v>
       </c>
       <c r="D29">
-        <v>47.33207639906002</v>
+        <v>47.36195145117198</v>
       </c>
       <c r="E29">
-        <v>4.287000000000006</v>
+        <v>5.768000000000008</v>
       </c>
       <c r="F29">
-        <v>39.98700000000001</v>
+        <v>41.46800000000001</v>
       </c>
       <c r="G29">
         <v>101.7</v>
@@ -3665,28 +3665,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M29">
-        <v>2.0113461</v>
+        <v>2.0858404</v>
       </c>
       <c r="N29">
-        <v>33.63151104285716</v>
+        <v>33.55701674285715</v>
       </c>
       <c r="O29">
-        <v>8.484563891434284</v>
+        <v>8.465770455507712</v>
       </c>
       <c r="P29">
-        <v>25.14694715142287</v>
+        <v>25.09124628734944</v>
       </c>
       <c r="Q29">
-        <v>61.64694715142287</v>
+        <v>61.59124628734943</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1984840768739019</v>
+        <v>0.2001856010413483</v>
       </c>
       <c r="T29">
-        <v>1.227813297849701</v>
+        <v>1.241496152291221</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>17.72089703649568</v>
+        <v>17.08800785662083</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1546645185975495</v>
+        <v>0.154280878295364</v>
       </c>
       <c r="C30">
-        <v>107.593951451172</v>
+        <v>106.1428642401635</v>
       </c>
       <c r="D30">
-        <v>47.36195145117198</v>
+        <v>47.39186424016354</v>
       </c>
       <c r="E30">
-        <v>5.768000000000008</v>
+        <v>7.249000000000009</v>
       </c>
       <c r="F30">
-        <v>41.46800000000001</v>
+        <v>42.94900000000001</v>
       </c>
       <c r="G30">
         <v>101.7</v>
@@ -3747,28 +3747,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M30">
-        <v>2.0858404</v>
+        <v>2.1603347</v>
       </c>
       <c r="N30">
-        <v>33.55701674285715</v>
+        <v>33.48252244285715</v>
       </c>
       <c r="O30">
-        <v>8.465770455507712</v>
+        <v>8.446977019581142</v>
       </c>
       <c r="P30">
-        <v>25.09124628734944</v>
+        <v>25.03554542327601</v>
       </c>
       <c r="Q30">
-        <v>61.59124628734943</v>
+        <v>61.53554542327601</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2001856010413483</v>
+        <v>0.2019350554670326</v>
       </c>
       <c r="T30">
-        <v>1.241496152291221</v>
+        <v>1.25556443925222</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>17.08800785662083</v>
+        <v>16.49876620639253</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.154280878295364</v>
+        <v>0.1538972379931785</v>
       </c>
       <c r="C31">
-        <v>106.1428642401635</v>
+        <v>104.6918148375813</v>
       </c>
       <c r="D31">
-        <v>47.39186424016354</v>
+        <v>47.42181483758129</v>
       </c>
       <c r="E31">
-        <v>7.249000000000002</v>
+        <v>8.730000000000004</v>
       </c>
       <c r="F31">
-        <v>42.94900000000001</v>
+        <v>44.43000000000001</v>
       </c>
       <c r="G31">
         <v>101.7</v>
@@ -3829,28 +3829,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M31">
-        <v>2.1603347</v>
+        <v>2.234829</v>
       </c>
       <c r="N31">
-        <v>33.48252244285715</v>
+        <v>33.40802814285716</v>
       </c>
       <c r="O31">
-        <v>8.446977019581142</v>
+        <v>8.428183583654572</v>
       </c>
       <c r="P31">
-        <v>25.03554542327601</v>
+        <v>24.97984455920258</v>
       </c>
       <c r="Q31">
-        <v>61.53554542327601</v>
+        <v>61.47984455920258</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2019350554670326</v>
+        <v>0.2037344943048794</v>
       </c>
       <c r="T31">
-        <v>1.25556443925222</v>
+        <v>1.270034677269247</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>16.49876620639253</v>
+        <v>15.94880733284611</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1538972379931785</v>
+        <v>0.153513597690993</v>
       </c>
       <c r="C32">
-        <v>104.6918148375813</v>
+        <v>103.2408033151528</v>
       </c>
       <c r="D32">
-        <v>47.42181483758129</v>
+        <v>47.45180331515281</v>
       </c>
       <c r="E32">
-        <v>8.730000000000004</v>
+        <v>10.21100000000001</v>
       </c>
       <c r="F32">
-        <v>44.43000000000001</v>
+        <v>45.91100000000001</v>
       </c>
       <c r="G32">
         <v>101.7</v>
@@ -3911,28 +3911,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M32">
-        <v>2.234829</v>
+        <v>2.3093233</v>
       </c>
       <c r="N32">
-        <v>33.40802814285716</v>
+        <v>33.33353384285715</v>
       </c>
       <c r="O32">
-        <v>8.428183583654572</v>
+        <v>8.409390147728001</v>
       </c>
       <c r="P32">
-        <v>24.97984455920258</v>
+        <v>24.92414369512915</v>
       </c>
       <c r="Q32">
-        <v>61.47984455920258</v>
+        <v>61.42414369512915</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2037344943048794</v>
+        <v>0.2055860907902</v>
       </c>
       <c r="T32">
-        <v>1.270034677269247</v>
+        <v>1.284924342475174</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>15.94880733284611</v>
+        <v>15.43432967694785</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.153513597690993</v>
+        <v>0.1531299573888076</v>
       </c>
       <c r="C33">
-        <v>103.2408033151528</v>
+        <v>101.7898297447872</v>
       </c>
       <c r="D33">
-        <v>47.45180331515281</v>
+        <v>47.4818297447872</v>
       </c>
       <c r="E33">
-        <v>10.21100000000001</v>
+        <v>11.69200000000001</v>
       </c>
       <c r="F33">
-        <v>45.91100000000001</v>
+        <v>47.39200000000001</v>
       </c>
       <c r="G33">
         <v>101.7</v>
@@ -3993,28 +3993,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M33">
-        <v>2.3093233</v>
+        <v>2.3838176</v>
       </c>
       <c r="N33">
-        <v>33.33353384285715</v>
+        <v>33.25903954285715</v>
       </c>
       <c r="O33">
-        <v>8.409390147728001</v>
+        <v>8.390596711801432</v>
       </c>
       <c r="P33">
-        <v>24.92414369512915</v>
+        <v>24.86844283105572</v>
       </c>
       <c r="Q33">
-        <v>61.42414369512915</v>
+        <v>61.36844283105572</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2055860907902</v>
+        <v>0.2074921459956771</v>
       </c>
       <c r="T33">
-        <v>1.284924342475174</v>
+        <v>1.300251939010687</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>15.43432967694785</v>
+        <v>14.95200687454323</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1531299573888076</v>
+        <v>0.1527463170866221</v>
       </c>
       <c r="C34">
-        <v>101.7898297447872</v>
+        <v>100.3388941985757</v>
       </c>
       <c r="D34">
-        <v>47.4818297447872</v>
+        <v>47.51189419857573</v>
       </c>
       <c r="E34">
-        <v>11.69200000000001</v>
+        <v>13.17300000000001</v>
       </c>
       <c r="F34">
-        <v>47.39200000000001</v>
+        <v>48.87300000000001</v>
       </c>
       <c r="G34">
         <v>101.7</v>
@@ -4075,28 +4075,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M34">
-        <v>2.3838176</v>
+        <v>2.4583119</v>
       </c>
       <c r="N34">
-        <v>33.25903954285715</v>
+        <v>33.18454524285715</v>
       </c>
       <c r="O34">
-        <v>8.390596711801432</v>
+        <v>8.371803275874862</v>
       </c>
       <c r="P34">
-        <v>24.86844283105572</v>
+        <v>24.81274196698229</v>
       </c>
       <c r="Q34">
-        <v>61.36844283105572</v>
+        <v>61.31274196698229</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2074921459956771</v>
+        <v>0.2094550983714669</v>
       </c>
       <c r="T34">
-        <v>1.300251939010687</v>
+        <v>1.316037075741289</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>14.95200687454323</v>
+        <v>14.49891575713283</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1527463170866221</v>
+        <v>0.1523626767844366</v>
       </c>
       <c r="C35">
-        <v>100.3388941985757</v>
+        <v>98.88799674879232</v>
       </c>
       <c r="D35">
-        <v>47.51189419857573</v>
+        <v>47.54199674879232</v>
       </c>
       <c r="E35">
-        <v>13.17300000000001</v>
+        <v>14.65400000000001</v>
       </c>
       <c r="F35">
-        <v>48.87300000000001</v>
+        <v>50.35400000000001</v>
       </c>
       <c r="G35">
         <v>101.7</v>
@@ -4157,28 +4157,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M35">
-        <v>2.4583119</v>
+        <v>2.5328062</v>
       </c>
       <c r="N35">
-        <v>33.18454524285715</v>
+        <v>33.11005094285715</v>
       </c>
       <c r="O35">
-        <v>8.371803275874862</v>
+        <v>8.353009839948291</v>
       </c>
       <c r="P35">
-        <v>24.81274196698229</v>
+        <v>24.75704110290886</v>
       </c>
       <c r="Q35">
-        <v>61.31274196698229</v>
+        <v>61.25704110290886</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2094550983714669</v>
+        <v>0.2114775341525837</v>
       </c>
       <c r="T35">
-        <v>1.316037075741289</v>
+        <v>1.332300549948577</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>14.49891575713283</v>
+        <v>14.07247705839363</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1523626767844366</v>
+        <v>0.1519790364822511</v>
       </c>
       <c r="C36">
-        <v>98.88799674879232</v>
+        <v>97.43713746789422</v>
       </c>
       <c r="D36">
-        <v>47.54199674879232</v>
+        <v>47.57213746789422</v>
       </c>
       <c r="E36">
-        <v>14.65400000000001</v>
+        <v>16.13500000000001</v>
       </c>
       <c r="F36">
-        <v>50.35400000000001</v>
+        <v>51.83500000000002</v>
       </c>
       <c r="G36">
         <v>101.7</v>
@@ -4239,28 +4239,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M36">
-        <v>2.5328062</v>
+        <v>2.6073005</v>
       </c>
       <c r="N36">
-        <v>33.11005094285715</v>
+        <v>33.03555664285715</v>
       </c>
       <c r="O36">
-        <v>8.353009839948291</v>
+        <v>8.334216404021721</v>
       </c>
       <c r="P36">
-        <v>24.75704110290886</v>
+        <v>24.70134023883543</v>
       </c>
       <c r="Q36">
-        <v>61.25704110290886</v>
+        <v>61.20134023883543</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2114775341525837</v>
+        <v>0.2135621987269656</v>
       </c>
       <c r="T36">
-        <v>1.332300549948577</v>
+        <v>1.349064438746858</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.07247705839363</v>
+        <v>13.67040628529667</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1519790364822511</v>
+        <v>0.1515953961800656</v>
       </c>
       <c r="C37">
-        <v>97.43713746789422</v>
+        <v>95.98631642852247</v>
       </c>
       <c r="D37">
-        <v>47.57213746789422</v>
+        <v>47.60231642852249</v>
       </c>
       <c r="E37">
-        <v>16.13500000000001</v>
+        <v>17.61600000000001</v>
       </c>
       <c r="F37">
-        <v>51.83500000000002</v>
+        <v>53.31600000000002</v>
       </c>
       <c r="G37">
         <v>101.7</v>
@@ -4321,28 +4321,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M37">
-        <v>2.6073005</v>
+        <v>2.681794800000001</v>
       </c>
       <c r="N37">
-        <v>33.03555664285715</v>
+        <v>32.96106234285715</v>
       </c>
       <c r="O37">
-        <v>8.334216404021721</v>
+        <v>8.315422968095152</v>
       </c>
       <c r="P37">
-        <v>24.70134023883543</v>
+        <v>24.645639374762</v>
       </c>
       <c r="Q37">
-        <v>61.20134023883543</v>
+        <v>61.145639374762</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2135621987269656</v>
+        <v>0.2157120090692969</v>
       </c>
       <c r="T37">
-        <v>1.349064438746858</v>
+        <v>1.366352199070086</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>13.67040628529667</v>
+        <v>13.29067277737176</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1515953961800656</v>
+        <v>0.1512117558778801</v>
       </c>
       <c r="C38">
-        <v>95.98631642852249</v>
+        <v>94.53553370350268</v>
       </c>
       <c r="D38">
-        <v>47.60231642852249</v>
+        <v>47.63253370350269</v>
       </c>
       <c r="E38">
-        <v>17.61600000000001</v>
+        <v>19.09700000000001</v>
       </c>
       <c r="F38">
-        <v>53.31600000000001</v>
+        <v>54.79700000000001</v>
       </c>
       <c r="G38">
         <v>101.7</v>
@@ -4403,28 +4403,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M38">
-        <v>2.6817948</v>
+        <v>2.7562891</v>
       </c>
       <c r="N38">
-        <v>32.96106234285715</v>
+        <v>32.88656804285715</v>
       </c>
       <c r="O38">
-        <v>8.315422968095152</v>
+        <v>8.296629532168581</v>
       </c>
       <c r="P38">
-        <v>24.645639374762</v>
+        <v>24.58993851068857</v>
       </c>
       <c r="Q38">
-        <v>61.145639374762</v>
+        <v>61.08993851068857</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2157120090692969</v>
+        <v>0.2179300673590039</v>
       </c>
       <c r="T38">
-        <v>1.366352199070086</v>
+        <v>1.384188777181352</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>13.29067277737176</v>
+        <v>12.93146540501036</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1512117558778801</v>
+        <v>0.1512543158691648</v>
       </c>
       <c r="C39">
-        <v>94.53553370350268</v>
+        <v>93.05117959106839</v>
       </c>
       <c r="D39">
-        <v>47.63253370350269</v>
+        <v>47.62917959106839</v>
       </c>
       <c r="E39">
-        <v>19.09700000000001</v>
+        <v>20.578</v>
       </c>
       <c r="F39">
-        <v>54.79700000000001</v>
+        <v>56.27800000000001</v>
       </c>
       <c r="G39">
         <v>101.7</v>
@@ -4485,45 +4485,45 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M39">
-        <v>2.7562891</v>
+        <v>2.9152004</v>
       </c>
       <c r="N39">
-        <v>32.88656804285715</v>
+        <v>32.72765674285715</v>
       </c>
       <c r="O39">
-        <v>8.296629532168581</v>
+        <v>8.256539359704943</v>
       </c>
       <c r="P39">
-        <v>24.58993851068857</v>
+        <v>24.4711173831522</v>
       </c>
       <c r="Q39">
-        <v>61.08993851068857</v>
+        <v>60.9711173831522</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2179300673590039</v>
+        <v>0.2202196759161207</v>
       </c>
       <c r="T39">
-        <v>1.384188777181352</v>
+        <v>1.402600728780079</v>
       </c>
       <c r="U39">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V39">
         <v>0.2522801868944358</v>
       </c>
       <c r="W39">
-        <v>0.03761030659920988</v>
+        <v>0.03873188631886822</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y39">
-        <v>12.93146540501036</v>
+        <v>12.2265546968425</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1512543158691648</v>
+        <v>0.1508818913641758</v>
       </c>
       <c r="C40">
-        <v>93.05117959106839</v>
+        <v>91.59954604048778</v>
       </c>
       <c r="D40">
-        <v>47.62917959106839</v>
+        <v>47.65854604048778</v>
       </c>
       <c r="E40">
-        <v>20.578</v>
+        <v>22.059</v>
       </c>
       <c r="F40">
-        <v>56.27800000000001</v>
+        <v>57.75900000000001</v>
       </c>
       <c r="G40">
         <v>101.7</v>
@@ -4567,28 +4567,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M40">
-        <v>2.9152004</v>
+        <v>2.9919162</v>
       </c>
       <c r="N40">
-        <v>32.72765674285715</v>
+        <v>32.65094094285715</v>
       </c>
       <c r="O40">
-        <v>8.256539359704943</v>
+        <v>8.237185483343188</v>
       </c>
       <c r="P40">
-        <v>24.4711173831522</v>
+        <v>24.41375545951396</v>
       </c>
       <c r="Q40">
-        <v>60.9711173831522</v>
+        <v>60.91375545951396</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2202196759161207</v>
+        <v>0.2225843536062578</v>
       </c>
       <c r="T40">
-        <v>1.402600728780079</v>
+        <v>1.421616350923026</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>12.2265546968425</v>
+        <v>11.91305329435936</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1508818913641758</v>
+        <v>0.150509466859187</v>
       </c>
       <c r="C41">
-        <v>91.59954604048778</v>
+        <v>90.1479487248541</v>
       </c>
       <c r="D41">
-        <v>47.65854604048778</v>
+        <v>47.68794872485412</v>
       </c>
       <c r="E41">
-        <v>22.059</v>
+        <v>23.54000000000001</v>
       </c>
       <c r="F41">
-        <v>57.75900000000001</v>
+        <v>59.24000000000001</v>
       </c>
       <c r="G41">
         <v>101.7</v>
@@ -4649,28 +4649,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M41">
-        <v>2.9919162</v>
+        <v>3.068632</v>
       </c>
       <c r="N41">
-        <v>32.65094094285715</v>
+        <v>32.57422514285715</v>
       </c>
       <c r="O41">
-        <v>8.237185483343188</v>
+        <v>8.217831606981431</v>
       </c>
       <c r="P41">
-        <v>24.41375545951396</v>
+        <v>24.35639353587572</v>
       </c>
       <c r="Q41">
-        <v>60.91375545951396</v>
+        <v>60.85639353587572</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2225843536062578</v>
+        <v>0.2250278538860661</v>
       </c>
       <c r="T41">
-        <v>1.421616350923026</v>
+        <v>1.441265827137405</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>11.91305329435936</v>
+        <v>11.61522696200038</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.150509466859187</v>
+        <v>0.150137042354198</v>
       </c>
       <c r="C42">
-        <v>90.1479487248541</v>
+        <v>88.69638771127364</v>
       </c>
       <c r="D42">
-        <v>47.68794872485412</v>
+        <v>47.71738771127365</v>
       </c>
       <c r="E42">
-        <v>23.54000000000001</v>
+        <v>25.02100000000001</v>
       </c>
       <c r="F42">
-        <v>59.24000000000001</v>
+        <v>60.72100000000001</v>
       </c>
       <c r="G42">
         <v>101.7</v>
@@ -4731,28 +4731,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M42">
-        <v>3.068632</v>
+        <v>3.145347800000001</v>
       </c>
       <c r="N42">
-        <v>32.57422514285715</v>
+        <v>32.49750934285715</v>
       </c>
       <c r="O42">
-        <v>8.217831606981431</v>
+        <v>8.198477730619674</v>
       </c>
       <c r="P42">
-        <v>24.35639353587572</v>
+        <v>24.29903161223748</v>
       </c>
       <c r="Q42">
-        <v>60.85639353587572</v>
+        <v>60.79903161223748</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2250278538860661</v>
+        <v>0.227554184683834</v>
       </c>
       <c r="T42">
-        <v>1.441265827137405</v>
+        <v>1.461581387291254</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>11.61522696200038</v>
+        <v>11.331928743415</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.150137042354198</v>
+        <v>0.1497646178492092</v>
       </c>
       <c r="C43">
-        <v>88.69638771127364</v>
+        <v>87.24486306701844</v>
       </c>
       <c r="D43">
-        <v>47.71738771127365</v>
+        <v>47.74686306701845</v>
       </c>
       <c r="E43">
-        <v>25.02100000000001</v>
+        <v>26.50200000000001</v>
       </c>
       <c r="F43">
-        <v>60.72100000000001</v>
+        <v>62.20200000000001</v>
       </c>
       <c r="G43">
         <v>101.7</v>
@@ -4813,28 +4813,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M43">
-        <v>3.145347800000001</v>
+        <v>3.222063600000001</v>
       </c>
       <c r="N43">
-        <v>32.49750934285715</v>
+        <v>32.42079354285715</v>
       </c>
       <c r="O43">
-        <v>8.198477730619674</v>
+        <v>8.179123854257918</v>
       </c>
       <c r="P43">
-        <v>24.29903161223748</v>
+        <v>24.24166968859924</v>
       </c>
       <c r="Q43">
-        <v>60.79903161223748</v>
+        <v>60.74166968859924</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.227554184683834</v>
+        <v>0.2301676303366974</v>
       </c>
       <c r="T43">
-        <v>1.461581387291254</v>
+        <v>1.482597484002133</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.331928743415</v>
+        <v>11.06212091619084</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1497646178492091</v>
+        <v>0.1493921933442202</v>
       </c>
       <c r="C44">
-        <v>87.24486306701846</v>
+        <v>85.79337485952691</v>
       </c>
       <c r="D44">
-        <v>47.74686306701845</v>
+        <v>47.77637485952692</v>
       </c>
       <c r="E44">
-        <v>26.502</v>
+        <v>27.983</v>
       </c>
       <c r="F44">
-        <v>62.20200000000001</v>
+        <v>63.68300000000001</v>
       </c>
       <c r="G44">
         <v>101.7</v>
@@ -4895,28 +4895,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M44">
-        <v>3.2220636</v>
+        <v>3.2987794</v>
       </c>
       <c r="N44">
-        <v>32.42079354285715</v>
+        <v>32.34407774285715</v>
       </c>
       <c r="O44">
-        <v>8.179123854257918</v>
+        <v>8.159769977896163</v>
       </c>
       <c r="P44">
-        <v>24.24166968859924</v>
+        <v>24.18430776496099</v>
       </c>
       <c r="Q44">
-        <v>60.74166968859924</v>
+        <v>60.68430776496099</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2301676303366974</v>
+        <v>0.2328727758370296</v>
       </c>
       <c r="T44">
-        <v>1.482597484002132</v>
+        <v>1.504350987615147</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.06212091619084</v>
+        <v>10.80486229023291</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1493921933442202</v>
+        <v>0.1490197688392313</v>
       </c>
       <c r="C45">
-        <v>85.79337485952691</v>
+        <v>84.34192315640431</v>
       </c>
       <c r="D45">
-        <v>47.77637485952692</v>
+        <v>47.8059231564043</v>
       </c>
       <c r="E45">
-        <v>27.983</v>
+        <v>29.46400000000001</v>
       </c>
       <c r="F45">
-        <v>63.68300000000001</v>
+        <v>65.16400000000002</v>
       </c>
       <c r="G45">
         <v>101.7</v>
@@ -4977,28 +4977,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M45">
-        <v>3.2987794</v>
+        <v>3.375495200000001</v>
       </c>
       <c r="N45">
-        <v>32.34407774285715</v>
+        <v>32.26736194285715</v>
       </c>
       <c r="O45">
-        <v>8.159769977896163</v>
+        <v>8.140416101534406</v>
       </c>
       <c r="P45">
-        <v>24.18430776496099</v>
+        <v>24.12694584132274</v>
       </c>
       <c r="Q45">
-        <v>60.68430776496099</v>
+        <v>60.62694584132274</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2328727758370296</v>
+        <v>0.2356745336766595</v>
       </c>
       <c r="T45">
-        <v>1.504350987615147</v>
+        <v>1.526881402071483</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>10.80486229023291</v>
+        <v>10.55929723818216</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1490197688392313</v>
+        <v>0.1486473443342424</v>
       </c>
       <c r="C46">
-        <v>84.34192315640431</v>
+        <v>82.89050802542317</v>
       </c>
       <c r="D46">
-        <v>47.8059231564043</v>
+        <v>47.83550802542317</v>
       </c>
       <c r="E46">
-        <v>29.46400000000001</v>
+        <v>30.94500000000001</v>
       </c>
       <c r="F46">
-        <v>65.16400000000002</v>
+        <v>66.64500000000001</v>
       </c>
       <c r="G46">
         <v>101.7</v>
@@ -5059,28 +5059,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M46">
-        <v>3.375495200000001</v>
+        <v>3.452211000000001</v>
       </c>
       <c r="N46">
-        <v>32.26736194285715</v>
+        <v>32.19064614285715</v>
       </c>
       <c r="O46">
-        <v>8.140416101534406</v>
+        <v>8.121062225172651</v>
       </c>
       <c r="P46">
-        <v>24.12694584132274</v>
+        <v>24.0695839176845</v>
       </c>
       <c r="Q46">
-        <v>60.62694584132274</v>
+        <v>60.5695839176845</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2356745336766595</v>
+        <v>0.2385781736195486</v>
       </c>
       <c r="T46">
-        <v>1.526881402071483</v>
+        <v>1.550231104326232</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.55929723818216</v>
+        <v>10.32464618844478</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1486473443342424</v>
+        <v>0.1482749198292535</v>
       </c>
       <c r="C47">
-        <v>82.89050802542317</v>
+        <v>81.43912953452396</v>
       </c>
       <c r="D47">
-        <v>47.83550802542317</v>
+        <v>47.86512953452399</v>
       </c>
       <c r="E47">
-        <v>30.94500000000001</v>
+        <v>32.42600000000002</v>
       </c>
       <c r="F47">
-        <v>66.64500000000001</v>
+        <v>68.12600000000002</v>
       </c>
       <c r="G47">
         <v>101.7</v>
@@ -5141,28 +5141,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M47">
-        <v>3.452211000000001</v>
+        <v>3.528926800000001</v>
       </c>
       <c r="N47">
-        <v>32.19064614285715</v>
+        <v>32.11393034285715</v>
       </c>
       <c r="O47">
-        <v>8.121062225172651</v>
+        <v>8.101708348810893</v>
       </c>
       <c r="P47">
-        <v>24.0695839176845</v>
+        <v>24.01222199404626</v>
       </c>
       <c r="Q47">
-        <v>60.5695839176845</v>
+        <v>60.51222199404626</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2385781736195486</v>
+        <v>0.2415893557825447</v>
       </c>
       <c r="T47">
-        <v>1.550231104326232</v>
+        <v>1.574445610368194</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.32464618844478</v>
+        <v>10.1001973582612</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1482749198292535</v>
+        <v>0.1479024953242646</v>
       </c>
       <c r="C48">
-        <v>81.43912953452396</v>
+        <v>79.98778775181559</v>
       </c>
       <c r="D48">
-        <v>47.86512953452399</v>
+        <v>47.89478775181558</v>
       </c>
       <c r="E48">
-        <v>32.42600000000002</v>
+        <v>33.90700000000001</v>
       </c>
       <c r="F48">
-        <v>68.12600000000002</v>
+        <v>69.60700000000001</v>
       </c>
       <c r="G48">
         <v>101.7</v>
@@ -5223,28 +5223,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M48">
-        <v>3.528926800000001</v>
+        <v>3.605642600000001</v>
       </c>
       <c r="N48">
-        <v>32.11393034285715</v>
+        <v>32.03721454285715</v>
       </c>
       <c r="O48">
-        <v>8.101708348810893</v>
+        <v>8.082354472449138</v>
       </c>
       <c r="P48">
-        <v>24.01222199404626</v>
+        <v>23.95486007040801</v>
       </c>
       <c r="Q48">
-        <v>60.51222199404626</v>
+        <v>60.45486007040801</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2415893557825447</v>
+        <v>0.2447141674611255</v>
       </c>
       <c r="T48">
-        <v>1.574445610368194</v>
+        <v>1.599573871355135</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.1001973582612</v>
+        <v>9.885299542127981</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1479024953242646</v>
+        <v>0.1481402101867698</v>
       </c>
       <c r="C49">
-        <v>79.98778775181559</v>
+        <v>78.48785296520097</v>
       </c>
       <c r="D49">
-        <v>47.89478775181558</v>
+        <v>47.87585296520098</v>
       </c>
       <c r="E49">
-        <v>33.90700000000001</v>
+        <v>35.38800000000002</v>
       </c>
       <c r="F49">
-        <v>69.60700000000001</v>
+        <v>71.08800000000002</v>
       </c>
       <c r="G49">
         <v>101.7</v>
@@ -5305,45 +5305,45 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M49">
-        <v>3.605642600000001</v>
+        <v>3.803208000000001</v>
       </c>
       <c r="N49">
-        <v>32.03721454285715</v>
+        <v>31.83964914285715</v>
       </c>
       <c r="O49">
-        <v>8.082354472449138</v>
+        <v>8.032512636413264</v>
       </c>
       <c r="P49">
-        <v>23.95486007040801</v>
+        <v>23.80713650644389</v>
       </c>
       <c r="Q49">
-        <v>60.45486007040801</v>
+        <v>60.30713650644389</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2447141674611255</v>
+        <v>0.2479591642042672</v>
       </c>
       <c r="T49">
-        <v>1.599573871355135</v>
+        <v>1.625668603918497</v>
       </c>
       <c r="U49">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V49">
         <v>0.2522801868944358</v>
       </c>
       <c r="W49">
-        <v>0.03873188631886822</v>
+        <v>0.04000301000114768</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>9.885299542127981</v>
+        <v>9.371787486473824</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1481402101867698</v>
+        <v>0.1477804969186037</v>
       </c>
       <c r="C50">
-        <v>78.48785296520099</v>
+        <v>77.03551115116025</v>
       </c>
       <c r="D50">
-        <v>47.87585296520098</v>
+        <v>47.90451115116026</v>
       </c>
       <c r="E50">
-        <v>35.38800000000001</v>
+        <v>36.86900000000001</v>
       </c>
       <c r="F50">
-        <v>71.08800000000001</v>
+        <v>72.56900000000002</v>
       </c>
       <c r="G50">
         <v>101.7</v>
@@ -5387,28 +5387,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M50">
-        <v>3.803208</v>
+        <v>3.882441500000001</v>
       </c>
       <c r="N50">
-        <v>31.83964914285715</v>
+        <v>31.76041564285715</v>
       </c>
       <c r="O50">
-        <v>8.032512636413264</v>
+        <v>8.012523594224962</v>
       </c>
       <c r="P50">
-        <v>23.80713650644389</v>
+        <v>23.74789204863219</v>
       </c>
       <c r="Q50">
-        <v>60.30713650644389</v>
+        <v>60.24789204863219</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2479591642042672</v>
+        <v>0.2513314157216496</v>
       </c>
       <c r="T50">
-        <v>1.625668603918497</v>
+        <v>1.652786659327481</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>9.371787486473828</v>
+        <v>9.180526517362114</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1477804969186037</v>
+        <v>0.1474207836504376</v>
       </c>
       <c r="C51">
-        <v>77.03551115116025</v>
+        <v>75.58320366689063</v>
       </c>
       <c r="D51">
-        <v>47.90451115116026</v>
+        <v>47.93320366689063</v>
       </c>
       <c r="E51">
-        <v>36.86900000000001</v>
+        <v>38.35000000000001</v>
       </c>
       <c r="F51">
-        <v>72.56900000000002</v>
+        <v>74.05000000000001</v>
       </c>
       <c r="G51">
         <v>101.7</v>
@@ -5469,28 +5469,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M51">
-        <v>3.882441500000001</v>
+        <v>3.961675000000001</v>
       </c>
       <c r="N51">
-        <v>31.76041564285715</v>
+        <v>31.68118214285715</v>
       </c>
       <c r="O51">
-        <v>8.012523594224962</v>
+        <v>7.992534552036664</v>
       </c>
       <c r="P51">
-        <v>23.74789204863219</v>
+        <v>23.68864759082049</v>
       </c>
       <c r="Q51">
-        <v>60.24789204863219</v>
+        <v>60.18864759082049</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2513314157216496</v>
+        <v>0.2548385572997275</v>
       </c>
       <c r="T51">
-        <v>1.652786659327481</v>
+        <v>1.680989436952825</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>9.180526517362114</v>
+        <v>8.996915987014873</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1474207836504376</v>
+        <v>0.1470610703822715</v>
       </c>
       <c r="C52">
-        <v>75.58320366689063</v>
+        <v>74.13093057411476</v>
       </c>
       <c r="D52">
-        <v>47.93320366689063</v>
+        <v>47.96193057411477</v>
       </c>
       <c r="E52">
-        <v>38.35000000000001</v>
+        <v>39.831</v>
       </c>
       <c r="F52">
-        <v>74.05000000000001</v>
+        <v>75.53100000000001</v>
       </c>
       <c r="G52">
         <v>101.7</v>
@@ -5551,28 +5551,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M52">
-        <v>3.961675000000001</v>
+        <v>4.0409085</v>
       </c>
       <c r="N52">
-        <v>31.68118214285715</v>
+        <v>31.60194864285715</v>
       </c>
       <c r="O52">
-        <v>7.992534552036664</v>
+        <v>7.972545509848363</v>
       </c>
       <c r="P52">
-        <v>23.68864759082049</v>
+        <v>23.62940313300879</v>
       </c>
       <c r="Q52">
-        <v>60.18864759082049</v>
+        <v>60.12940313300879</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2548385572997275</v>
+        <v>0.2584888475136452</v>
       </c>
       <c r="T52">
-        <v>1.680989436952825</v>
+        <v>1.710343348358795</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.996915987014873</v>
+        <v>8.820505869622425</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1470610703822715</v>
+        <v>0.1467013571141054</v>
       </c>
       <c r="C53">
-        <v>74.13093057411476</v>
+        <v>72.67869193470337</v>
       </c>
       <c r="D53">
-        <v>47.96193057411477</v>
+        <v>47.99069193470338</v>
       </c>
       <c r="E53">
-        <v>39.831</v>
+        <v>41.31200000000001</v>
       </c>
       <c r="F53">
-        <v>75.53100000000001</v>
+        <v>77.01200000000001</v>
       </c>
       <c r="G53">
         <v>101.7</v>
@@ -5633,28 +5633,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M53">
-        <v>4.0409085</v>
+        <v>4.120142</v>
       </c>
       <c r="N53">
-        <v>31.60194864285715</v>
+        <v>31.52271514285715</v>
       </c>
       <c r="O53">
-        <v>7.972545509848363</v>
+        <v>7.952556467660063</v>
       </c>
       <c r="P53">
-        <v>23.62940313300879</v>
+        <v>23.57015867519709</v>
       </c>
       <c r="Q53">
-        <v>60.12940313300879</v>
+        <v>60.07015867519709</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2584888475136452</v>
+        <v>0.2622912331531428</v>
       </c>
       <c r="T53">
-        <v>1.710343348358795</v>
+        <v>1.74092033940668</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>8.820505869622425</v>
+        <v>8.650880756745071</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1467013571141054</v>
+        <v>0.1463416438459392</v>
       </c>
       <c r="C54">
-        <v>72.67869193470337</v>
+        <v>71.22648781067564</v>
       </c>
       <c r="D54">
-        <v>47.99069193470338</v>
+        <v>48.01948781067565</v>
       </c>
       <c r="E54">
-        <v>41.31200000000001</v>
+        <v>42.79300000000001</v>
       </c>
       <c r="F54">
-        <v>77.01200000000001</v>
+        <v>78.49300000000001</v>
       </c>
       <c r="G54">
         <v>101.7</v>
@@ -5715,28 +5715,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M54">
-        <v>4.120142</v>
+        <v>4.1993755</v>
       </c>
       <c r="N54">
-        <v>31.52271514285715</v>
+        <v>31.44348164285715</v>
       </c>
       <c r="O54">
-        <v>7.952556467660063</v>
+        <v>7.932567425471762</v>
       </c>
       <c r="P54">
-        <v>23.57015867519709</v>
+        <v>23.51091421738539</v>
       </c>
       <c r="Q54">
-        <v>60.07015867519709</v>
+        <v>60.01091421738539</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2622912331531428</v>
+        <v>0.2662554224368744</v>
       </c>
       <c r="T54">
-        <v>1.74092033940668</v>
+        <v>1.772798479009795</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.650880756745071</v>
+        <v>8.487656591523464</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1463416438459392</v>
+        <v>0.1459819305777731</v>
       </c>
       <c r="C55">
-        <v>71.22648781067564</v>
+        <v>69.77431826419971</v>
       </c>
       <c r="D55">
-        <v>48.01948781067565</v>
+        <v>48.04831826419974</v>
       </c>
       <c r="E55">
-        <v>42.79300000000001</v>
+        <v>44.27400000000002</v>
       </c>
       <c r="F55">
-        <v>78.49300000000001</v>
+        <v>79.97400000000002</v>
       </c>
       <c r="G55">
         <v>101.7</v>
@@ -5797,28 +5797,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M55">
-        <v>4.1993755</v>
+        <v>4.278609000000001</v>
       </c>
       <c r="N55">
-        <v>31.44348164285715</v>
+        <v>31.36424814285715</v>
       </c>
       <c r="O55">
-        <v>7.932567425471762</v>
+        <v>7.912578383283462</v>
       </c>
       <c r="P55">
-        <v>23.51091421738539</v>
+        <v>23.45166975957369</v>
       </c>
       <c r="Q55">
-        <v>60.01091421738539</v>
+        <v>59.95166975957369</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2662554224368744</v>
+        <v>0.2703919677764204</v>
       </c>
       <c r="T55">
-        <v>1.772798479009795</v>
+        <v>1.80606262468261</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.487656591523464</v>
+        <v>8.330477765754511</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1459819305777731</v>
+        <v>0.145622217309607</v>
       </c>
       <c r="C56">
-        <v>69.77431826419971</v>
+        <v>68.32218335759316</v>
       </c>
       <c r="D56">
-        <v>48.04831826419974</v>
+        <v>48.07718335759317</v>
       </c>
       <c r="E56">
-        <v>44.27400000000002</v>
+        <v>45.75500000000001</v>
       </c>
       <c r="F56">
-        <v>79.97400000000002</v>
+        <v>81.45500000000001</v>
       </c>
       <c r="G56">
         <v>101.7</v>
@@ -5879,28 +5879,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M56">
-        <v>4.278609000000001</v>
+        <v>4.3578425</v>
       </c>
       <c r="N56">
-        <v>31.36424814285715</v>
+        <v>31.28501464285715</v>
       </c>
       <c r="O56">
-        <v>7.912578383283462</v>
+        <v>7.892589341095162</v>
       </c>
       <c r="P56">
-        <v>23.45166975957369</v>
+        <v>23.39242530176199</v>
       </c>
       <c r="Q56">
-        <v>59.95166975957369</v>
+        <v>59.89242530176199</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2703919677764204</v>
+        <v>0.2747123595755018</v>
       </c>
       <c r="T56">
-        <v>1.80606262468261</v>
+        <v>1.840805176829772</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.330477765754511</v>
+        <v>8.179014533649886</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.145622217309607</v>
+        <v>0.1452625040414409</v>
       </c>
       <c r="C57">
-        <v>68.32218335759316</v>
+        <v>66.87008315332331</v>
       </c>
       <c r="D57">
-        <v>48.07718335759317</v>
+        <v>48.10608315332333</v>
       </c>
       <c r="E57">
-        <v>45.75500000000001</v>
+        <v>47.23600000000002</v>
       </c>
       <c r="F57">
-        <v>81.45500000000001</v>
+        <v>82.93600000000002</v>
       </c>
       <c r="G57">
         <v>101.7</v>
@@ -5961,28 +5961,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M57">
-        <v>4.3578425</v>
+        <v>4.437076000000001</v>
       </c>
       <c r="N57">
-        <v>31.28501464285715</v>
+        <v>31.20578114285715</v>
       </c>
       <c r="O57">
-        <v>7.892589341095162</v>
+        <v>7.872600298906861</v>
       </c>
       <c r="P57">
-        <v>23.39242530176199</v>
+        <v>23.33318084395029</v>
       </c>
       <c r="Q57">
-        <v>59.89242530176199</v>
+        <v>59.83318084395029</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2747123595755018</v>
+        <v>0.2792291328199959</v>
       </c>
       <c r="T57">
-        <v>1.840805176829772</v>
+        <v>1.877126935892715</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.179014533649886</v>
+        <v>8.032960702691851</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1452625040414409</v>
+        <v>0.1449027907732748</v>
       </c>
       <c r="C58">
-        <v>66.87008315332331</v>
+        <v>65.41801771400786</v>
       </c>
       <c r="D58">
-        <v>48.10608315332333</v>
+        <v>48.13501771400787</v>
       </c>
       <c r="E58">
-        <v>47.23600000000002</v>
+        <v>48.71700000000001</v>
       </c>
       <c r="F58">
-        <v>82.93600000000002</v>
+        <v>84.41700000000002</v>
       </c>
       <c r="G58">
         <v>101.7</v>
@@ -6043,28 +6043,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M58">
-        <v>4.437076000000001</v>
+        <v>4.516309500000001</v>
       </c>
       <c r="N58">
-        <v>31.20578114285715</v>
+        <v>31.12654764285715</v>
       </c>
       <c r="O58">
-        <v>7.872600298906861</v>
+        <v>7.852611256718562</v>
       </c>
       <c r="P58">
-        <v>23.33318084395029</v>
+        <v>23.27393638613859</v>
       </c>
       <c r="Q58">
-        <v>59.83318084395029</v>
+        <v>59.77393638613859</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2792291328199959</v>
+        <v>0.2839559885409781</v>
       </c>
       <c r="T58">
-        <v>1.877126935892715</v>
+        <v>1.91513807909812</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.032960702691851</v>
+        <v>7.892031567556906</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1449027907732748</v>
+        <v>0.1445430775051086</v>
       </c>
       <c r="C59">
-        <v>65.41801771400786</v>
+        <v>63.9659871024152</v>
       </c>
       <c r="D59">
-        <v>48.13501771400787</v>
+        <v>48.16398710241523</v>
       </c>
       <c r="E59">
-        <v>48.71700000000001</v>
+        <v>50.19800000000002</v>
       </c>
       <c r="F59">
-        <v>84.41700000000002</v>
+        <v>85.89800000000002</v>
       </c>
       <c r="G59">
         <v>101.7</v>
@@ -6125,28 +6125,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M59">
-        <v>4.516309500000001</v>
+        <v>4.595543000000001</v>
       </c>
       <c r="N59">
-        <v>31.12654764285715</v>
+        <v>31.04731414285715</v>
       </c>
       <c r="O59">
-        <v>7.852611256718562</v>
+        <v>7.832622214530262</v>
       </c>
       <c r="P59">
-        <v>23.27393638613859</v>
+        <v>23.21469192832689</v>
       </c>
       <c r="Q59">
-        <v>59.77393638613859</v>
+        <v>59.71469192832689</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2839559885409781</v>
+        <v>0.2889079326296262</v>
       </c>
       <c r="T59">
-        <v>1.91513807909812</v>
+        <v>1.954959276741878</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>7.892031567556906</v>
+        <v>7.755962057771442</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1445430775051086</v>
+        <v>0.1441833642369425</v>
       </c>
       <c r="C60">
-        <v>63.96598710241521</v>
+        <v>62.51399138146495</v>
       </c>
       <c r="D60">
-        <v>48.16398710241523</v>
+        <v>48.19299138146496</v>
       </c>
       <c r="E60">
-        <v>50.19800000000001</v>
+        <v>51.679</v>
       </c>
       <c r="F60">
-        <v>85.89800000000001</v>
+        <v>87.379</v>
       </c>
       <c r="G60">
         <v>101.7</v>
@@ -6207,28 +6207,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M60">
-        <v>4.595543</v>
+        <v>4.6747765</v>
       </c>
       <c r="N60">
-        <v>31.04731414285715</v>
+        <v>30.96808064285715</v>
       </c>
       <c r="O60">
-        <v>7.832622214530262</v>
+        <v>7.812633172341961</v>
       </c>
       <c r="P60">
-        <v>23.21469192832689</v>
+        <v>23.15544747051519</v>
       </c>
       <c r="Q60">
-        <v>59.71469192832689</v>
+        <v>59.65544747051519</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2889079326296262</v>
+        <v>0.294101434966501</v>
       </c>
       <c r="T60">
-        <v>1.954959276741877</v>
+        <v>1.996722971831672</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>7.755962057771444</v>
+        <v>7.624505073741419</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1441833642369425</v>
+        <v>0.1441825564790671</v>
       </c>
       <c r="C61">
-        <v>62.51399138146495</v>
+        <v>61.03305655163564</v>
       </c>
       <c r="D61">
-        <v>48.19299138146496</v>
+        <v>48.19305655163566</v>
       </c>
       <c r="E61">
-        <v>51.679</v>
+        <v>53.16000000000001</v>
       </c>
       <c r="F61">
-        <v>87.379</v>
+        <v>88.86000000000001</v>
       </c>
       <c r="G61">
         <v>101.7</v>
@@ -6289,45 +6289,45 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M61">
-        <v>4.6747765</v>
+        <v>4.825098000000001</v>
       </c>
       <c r="N61">
-        <v>30.96808064285715</v>
+        <v>30.81775914285715</v>
       </c>
       <c r="O61">
-        <v>7.812633172341961</v>
+        <v>7.774710036227709</v>
       </c>
       <c r="P61">
-        <v>23.15544747051519</v>
+        <v>23.04304910662944</v>
       </c>
       <c r="Q61">
-        <v>59.65544747051519</v>
+        <v>59.54304910662944</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.294101434966501</v>
+        <v>0.2995546124202195</v>
       </c>
       <c r="T61">
-        <v>1.996722971831672</v>
+        <v>2.040574851675955</v>
       </c>
       <c r="U61">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V61">
         <v>0.2522801868944358</v>
       </c>
       <c r="W61">
-        <v>0.04000301000114768</v>
+        <v>0.04060118585163214</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y61">
-        <v>7.624505073741419</v>
+        <v>7.386970615489498</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1441825564790671</v>
+        <v>0.1438288249694059</v>
       </c>
       <c r="C62">
-        <v>61.03305655163564</v>
+        <v>59.58061267512755</v>
       </c>
       <c r="D62">
-        <v>48.19305655163566</v>
+        <v>48.22161267512755</v>
       </c>
       <c r="E62">
-        <v>53.16000000000001</v>
+        <v>54.64100000000001</v>
       </c>
       <c r="F62">
-        <v>88.86000000000001</v>
+        <v>90.34100000000001</v>
       </c>
       <c r="G62">
         <v>101.7</v>
@@ -6371,28 +6371,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M62">
-        <v>4.825098000000001</v>
+        <v>4.9055163</v>
       </c>
       <c r="N62">
-        <v>30.81775914285715</v>
+        <v>30.73734084285715</v>
       </c>
       <c r="O62">
-        <v>7.774710036227709</v>
+        <v>7.754422092473976</v>
       </c>
       <c r="P62">
-        <v>23.04304910662944</v>
+        <v>22.98291875038317</v>
       </c>
       <c r="Q62">
-        <v>59.54304910662944</v>
+        <v>59.48291875038318</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2995546124202195</v>
+        <v>0.3052874399997698</v>
       </c>
       <c r="T62">
-        <v>2.040574851675955</v>
+        <v>2.086675545871229</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.386970615489498</v>
+        <v>7.265872736547048</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1438288249694059</v>
+        <v>0.1434750934597445</v>
       </c>
       <c r="C63">
-        <v>59.58061267512755</v>
+        <v>58.12820265974874</v>
       </c>
       <c r="D63">
-        <v>48.22161267512755</v>
+        <v>48.25020265974874</v>
       </c>
       <c r="E63">
-        <v>54.64100000000001</v>
+        <v>56.12200000000001</v>
       </c>
       <c r="F63">
-        <v>90.34100000000001</v>
+        <v>91.82200000000002</v>
       </c>
       <c r="G63">
         <v>101.7</v>
@@ -6453,28 +6453,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M63">
-        <v>4.9055163</v>
+        <v>4.985934600000001</v>
       </c>
       <c r="N63">
-        <v>30.73734084285715</v>
+        <v>30.65692254285715</v>
       </c>
       <c r="O63">
-        <v>7.754422092473976</v>
+        <v>7.734134148720243</v>
       </c>
       <c r="P63">
-        <v>22.98291875038317</v>
+        <v>22.92278839413691</v>
       </c>
       <c r="Q63">
-        <v>59.48291875038318</v>
+        <v>59.42278839413691</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3052874399997698</v>
+        <v>0.3113219953466648</v>
       </c>
       <c r="T63">
-        <v>2.086675545871229</v>
+        <v>2.135202592392569</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.265872736547048</v>
+        <v>7.148681240796289</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1434750934597445</v>
+        <v>0.1431213619500833</v>
       </c>
       <c r="C64">
-        <v>58.12820265974874</v>
+        <v>56.67582656576251</v>
       </c>
       <c r="D64">
-        <v>48.25020265974874</v>
+        <v>48.2788265657625</v>
       </c>
       <c r="E64">
-        <v>56.12200000000001</v>
+        <v>57.60300000000001</v>
       </c>
       <c r="F64">
-        <v>91.82200000000002</v>
+        <v>93.30300000000001</v>
       </c>
       <c r="G64">
         <v>101.7</v>
@@ -6535,28 +6535,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M64">
-        <v>4.985934600000001</v>
+        <v>5.066352900000001</v>
       </c>
       <c r="N64">
-        <v>30.65692254285715</v>
+        <v>30.57650424285715</v>
       </c>
       <c r="O64">
-        <v>7.734134148720243</v>
+        <v>7.713846204966511</v>
       </c>
       <c r="P64">
-        <v>22.92278839413691</v>
+        <v>22.86265803789064</v>
       </c>
       <c r="Q64">
-        <v>59.42278839413691</v>
+        <v>59.36265803789064</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3113219953466648</v>
+        <v>0.3176827428744731</v>
       </c>
       <c r="T64">
-        <v>2.135202592392569</v>
+        <v>2.186352722509658</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.148681240796289</v>
+        <v>7.035210109989998</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1431213619500833</v>
+        <v>0.142767630440422</v>
       </c>
       <c r="C65">
-        <v>56.67582656576251</v>
+        <v>55.22348445357514</v>
       </c>
       <c r="D65">
-        <v>48.2788265657625</v>
+        <v>48.30748445357514</v>
       </c>
       <c r="E65">
-        <v>57.60300000000001</v>
+        <v>59.08400000000002</v>
       </c>
       <c r="F65">
-        <v>93.30300000000001</v>
+        <v>94.78400000000002</v>
       </c>
       <c r="G65">
         <v>101.7</v>
@@ -6617,28 +6617,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M65">
-        <v>5.066352900000001</v>
+        <v>5.146771200000001</v>
       </c>
       <c r="N65">
-        <v>30.57650424285715</v>
+        <v>30.49608594285715</v>
       </c>
       <c r="O65">
-        <v>7.713846204966511</v>
+        <v>7.693558261212778</v>
       </c>
       <c r="P65">
-        <v>22.86265803789064</v>
+        <v>22.80252768164437</v>
       </c>
       <c r="Q65">
-        <v>59.36265803789064</v>
+        <v>59.30252768164438</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3176827428744731</v>
+        <v>0.3243968652649374</v>
       </c>
       <c r="T65">
-        <v>2.186352722509658</v>
+        <v>2.24034452652214</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.035210109989998</v>
+        <v>6.925284952021405</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.142767630440422</v>
+        <v>0.1424138989307608</v>
       </c>
       <c r="C66">
-        <v>55.22348445357514</v>
+        <v>53.7711763837365</v>
       </c>
       <c r="D66">
-        <v>48.30748445357514</v>
+        <v>48.3361763837365</v>
       </c>
       <c r="E66">
-        <v>59.08400000000002</v>
+        <v>60.56500000000001</v>
       </c>
       <c r="F66">
-        <v>94.78400000000002</v>
+        <v>96.26500000000001</v>
       </c>
       <c r="G66">
         <v>101.7</v>
@@ -6699,28 +6699,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M66">
-        <v>5.146771200000001</v>
+        <v>5.227189500000001</v>
       </c>
       <c r="N66">
-        <v>30.49608594285715</v>
+        <v>30.41566764285715</v>
       </c>
       <c r="O66">
-        <v>7.693558261212778</v>
+        <v>7.673270317459044</v>
       </c>
       <c r="P66">
-        <v>22.80252768164437</v>
+        <v>22.74239732539811</v>
       </c>
       <c r="Q66">
-        <v>59.30252768164438</v>
+        <v>59.24239732539811</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3243968652649374</v>
+        <v>0.3314946517919997</v>
       </c>
       <c r="T66">
-        <v>2.24034452652214</v>
+        <v>2.297421576478193</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.925284952021405</v>
+        <v>6.818742106605691</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1424138989307608</v>
+        <v>0.1420601674210995</v>
       </c>
       <c r="C67">
-        <v>53.7711763837365</v>
+        <v>52.31890241694033</v>
       </c>
       <c r="D67">
-        <v>48.3361763837365</v>
+        <v>48.36490241694034</v>
       </c>
       <c r="E67">
-        <v>60.56500000000001</v>
+        <v>62.04600000000002</v>
       </c>
       <c r="F67">
-        <v>96.26500000000001</v>
+        <v>97.74600000000002</v>
       </c>
       <c r="G67">
         <v>101.7</v>
@@ -6781,28 +6781,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M67">
-        <v>5.227189500000001</v>
+        <v>5.307607800000001</v>
       </c>
       <c r="N67">
-        <v>30.41566764285715</v>
+        <v>30.33524934285715</v>
       </c>
       <c r="O67">
-        <v>7.673270317459044</v>
+        <v>7.652982373705313</v>
       </c>
       <c r="P67">
-        <v>22.74239732539811</v>
+        <v>22.68226696915184</v>
       </c>
       <c r="Q67">
-        <v>59.24239732539811</v>
+        <v>59.18226696915184</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3314946517919997</v>
+        <v>0.3390099551735949</v>
       </c>
       <c r="T67">
-        <v>2.297421576478193</v>
+        <v>2.357856099961071</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.818742106605691</v>
+        <v>6.71542783226318</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1420601674210995</v>
+        <v>0.1417064359114382</v>
       </c>
       <c r="C68">
-        <v>52.31890241694033</v>
+        <v>50.8666626140248</v>
       </c>
       <c r="D68">
-        <v>48.36490241694034</v>
+        <v>48.39366261402481</v>
       </c>
       <c r="E68">
-        <v>62.04600000000002</v>
+        <v>63.52700000000002</v>
       </c>
       <c r="F68">
-        <v>97.74600000000002</v>
+        <v>99.22700000000002</v>
       </c>
       <c r="G68">
         <v>101.7</v>
@@ -6863,28 +6863,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M68">
-        <v>5.307607800000001</v>
+        <v>5.388026100000001</v>
       </c>
       <c r="N68">
-        <v>30.33524934285715</v>
+        <v>30.25483104285715</v>
       </c>
       <c r="O68">
-        <v>7.652982373705313</v>
+        <v>7.632694429951579</v>
       </c>
       <c r="P68">
-        <v>22.68226696915184</v>
+        <v>22.62213661290557</v>
       </c>
       <c r="Q68">
-        <v>59.18226696915184</v>
+        <v>59.12213661290557</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3390099551735949</v>
+        <v>0.3469807314874082</v>
       </c>
       <c r="T68">
-        <v>2.357856099961071</v>
+        <v>2.421953321836853</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.71542783226318</v>
+        <v>6.615197566109998</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1417064359114382</v>
+        <v>0.1413527044017769</v>
       </c>
       <c r="C69">
-        <v>50.8666626140248</v>
+        <v>49.41445703597282</v>
       </c>
       <c r="D69">
-        <v>48.39366261402481</v>
+        <v>48.42245703597285</v>
       </c>
       <c r="E69">
-        <v>63.52700000000002</v>
+        <v>65.00800000000002</v>
       </c>
       <c r="F69">
-        <v>99.22700000000002</v>
+        <v>100.708</v>
       </c>
       <c r="G69">
         <v>101.7</v>
@@ -6945,28 +6945,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M69">
-        <v>5.388026100000001</v>
+        <v>5.468444400000002</v>
       </c>
       <c r="N69">
-        <v>30.25483104285715</v>
+        <v>30.17441274285715</v>
       </c>
       <c r="O69">
-        <v>7.632694429951579</v>
+        <v>7.612406486197846</v>
       </c>
       <c r="P69">
-        <v>22.62213661290557</v>
+        <v>22.56200625665931</v>
       </c>
       <c r="Q69">
-        <v>59.12213661290557</v>
+        <v>59.0620062566593</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3469807314874082</v>
+        <v>0.3554496813208347</v>
       </c>
       <c r="T69">
-        <v>2.421953321836853</v>
+        <v>2.49005662007987</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.615197566109998</v>
+        <v>6.51791524896132</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1413527044017769</v>
+        <v>0.1409989728921157</v>
       </c>
       <c r="C70">
-        <v>49.41445703597282</v>
+        <v>47.96228574391262</v>
       </c>
       <c r="D70">
-        <v>48.42245703597285</v>
+        <v>48.45128574391262</v>
       </c>
       <c r="E70">
-        <v>65.00800000000002</v>
+        <v>66.48900000000002</v>
       </c>
       <c r="F70">
-        <v>100.708</v>
+        <v>102.189</v>
       </c>
       <c r="G70">
         <v>101.7</v>
@@ -7027,28 +7027,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M70">
-        <v>5.468444400000002</v>
+        <v>5.548862700000002</v>
       </c>
       <c r="N70">
-        <v>30.17441274285715</v>
+        <v>30.09399444285715</v>
       </c>
       <c r="O70">
-        <v>7.612406486197846</v>
+        <v>7.592118542444114</v>
       </c>
       <c r="P70">
-        <v>22.56200625665931</v>
+        <v>22.50187590041304</v>
       </c>
       <c r="Q70">
-        <v>59.0620062566593</v>
+        <v>59.00187590041304</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3554496813208347</v>
+        <v>0.3644650150144823</v>
       </c>
       <c r="T70">
-        <v>2.49005662007987</v>
+        <v>2.562553679499856</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.51791524896132</v>
+        <v>6.423452709121302</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1409989728921157</v>
+        <v>0.1406452413824544</v>
       </c>
       <c r="C71">
-        <v>47.96228574391262</v>
+        <v>46.51014879911791</v>
       </c>
       <c r="D71">
-        <v>48.45128574391262</v>
+        <v>48.48014879911793</v>
       </c>
       <c r="E71">
-        <v>66.48900000000002</v>
+        <v>67.97000000000003</v>
       </c>
       <c r="F71">
-        <v>102.189</v>
+        <v>103.67</v>
       </c>
       <c r="G71">
         <v>101.7</v>
@@ -7109,28 +7109,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M71">
-        <v>5.548862700000002</v>
+        <v>5.629281000000002</v>
       </c>
       <c r="N71">
-        <v>30.09399444285715</v>
+        <v>30.01357614285715</v>
       </c>
       <c r="O71">
-        <v>7.592118542444114</v>
+        <v>7.57183059869038</v>
       </c>
       <c r="P71">
-        <v>22.50187590041304</v>
+        <v>22.44174554416677</v>
       </c>
       <c r="Q71">
-        <v>59.00187590041304</v>
+        <v>58.94174554416677</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3644650150144823</v>
+        <v>0.374081370954373</v>
       </c>
       <c r="T71">
-        <v>2.562553679499856</v>
+        <v>2.639883876214508</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.423452709121302</v>
+        <v>6.331689098990998</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1406452413824544</v>
+        <v>0.1402915098727932</v>
       </c>
       <c r="C72">
-        <v>46.51014879911791</v>
+        <v>45.05804626300868</v>
       </c>
       <c r="D72">
-        <v>48.48014879911793</v>
+        <v>48.5090462630087</v>
       </c>
       <c r="E72">
-        <v>67.97000000000003</v>
+        <v>69.45100000000002</v>
       </c>
       <c r="F72">
-        <v>103.67</v>
+        <v>105.151</v>
       </c>
       <c r="G72">
         <v>101.7</v>
@@ -7191,28 +7191,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M72">
-        <v>5.629281000000002</v>
+        <v>5.709699300000001</v>
       </c>
       <c r="N72">
-        <v>30.01357614285715</v>
+        <v>29.93315784285715</v>
       </c>
       <c r="O72">
-        <v>7.57183059869038</v>
+        <v>7.551542654936648</v>
       </c>
       <c r="P72">
-        <v>22.44174554416677</v>
+        <v>22.3816151879205</v>
       </c>
       <c r="Q72">
-        <v>58.94174554416677</v>
+        <v>58.8816151879205</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.374081370954373</v>
+        <v>0.3843609238556357</v>
       </c>
       <c r="T72">
-        <v>2.639883876214508</v>
+        <v>2.722547189943964</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.331689098990998</v>
+        <v>6.2425103792869</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1402915098727932</v>
+        <v>0.1399377783631318</v>
       </c>
       <c r="C73">
-        <v>45.05804626300869</v>
+        <v>43.60597819715137</v>
       </c>
       <c r="D73">
-        <v>48.5090462630087</v>
+        <v>48.53797819715138</v>
       </c>
       <c r="E73">
-        <v>69.45100000000001</v>
+        <v>70.93200000000002</v>
       </c>
       <c r="F73">
-        <v>105.151</v>
+        <v>106.632</v>
       </c>
       <c r="G73">
         <v>101.7</v>
@@ -7273,28 +7273,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M73">
-        <v>5.7096993</v>
+        <v>5.790117600000001</v>
       </c>
       <c r="N73">
-        <v>29.93315784285715</v>
+        <v>29.85273954285715</v>
       </c>
       <c r="O73">
-        <v>7.551542654936648</v>
+        <v>7.531254711182915</v>
       </c>
       <c r="P73">
-        <v>22.3816151879205</v>
+        <v>22.32148483167424</v>
       </c>
       <c r="Q73">
-        <v>58.8816151879205</v>
+        <v>58.82148483167424</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3843609238556355</v>
+        <v>0.3953747305355597</v>
       </c>
       <c r="T73">
-        <v>2.722547189943962</v>
+        <v>2.811115026082665</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.242510379286901</v>
+        <v>6.155808846241248</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1399377783631318</v>
+        <v>0.1401298823170377</v>
       </c>
       <c r="C74">
-        <v>43.60597819715137</v>
+        <v>42.10926160718627</v>
       </c>
       <c r="D74">
-        <v>48.53797819715138</v>
+        <v>48.52226160718627</v>
       </c>
       <c r="E74">
-        <v>70.93200000000002</v>
+        <v>72.41300000000001</v>
       </c>
       <c r="F74">
-        <v>106.632</v>
+        <v>108.113</v>
       </c>
       <c r="G74">
         <v>101.7</v>
@@ -7355,45 +7355,45 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M74">
-        <v>5.790117600000001</v>
+        <v>5.978648900000001</v>
       </c>
       <c r="N74">
-        <v>29.85273954285715</v>
+        <v>29.66420824285715</v>
       </c>
       <c r="O74">
-        <v>7.531254711182915</v>
+        <v>7.483691999583463</v>
       </c>
       <c r="P74">
-        <v>22.32148483167424</v>
+        <v>22.18051624327369</v>
       </c>
       <c r="Q74">
-        <v>58.82148483167424</v>
+        <v>58.68051624327369</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3953747305355597</v>
+        <v>0.4072043747473301</v>
       </c>
       <c r="T74">
-        <v>2.811115026082665</v>
+        <v>2.906243442676085</v>
       </c>
       <c r="U74">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V74">
         <v>0.2522801868944358</v>
       </c>
       <c r="W74">
-        <v>0.04060118585163214</v>
+        <v>0.0413489056647377</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>6.155808846241248</v>
+        <v>5.96169096714429</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1401298823170377</v>
+        <v>0.1397836280055074</v>
       </c>
       <c r="C75">
-        <v>42.10926160718627</v>
+        <v>40.65659705639027</v>
       </c>
       <c r="D75">
-        <v>48.52226160718627</v>
+        <v>48.5505970563903</v>
       </c>
       <c r="E75">
-        <v>72.41300000000001</v>
+        <v>73.89400000000002</v>
       </c>
       <c r="F75">
-        <v>108.113</v>
+        <v>109.594</v>
       </c>
       <c r="G75">
         <v>101.7</v>
@@ -7437,28 +7437,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M75">
-        <v>5.978648900000001</v>
+        <v>6.060548200000001</v>
       </c>
       <c r="N75">
-        <v>29.66420824285715</v>
+        <v>29.58230894285715</v>
       </c>
       <c r="O75">
-        <v>7.483691999583463</v>
+        <v>7.463030428872941</v>
       </c>
       <c r="P75">
-        <v>22.18051624327369</v>
+        <v>22.11927851398421</v>
       </c>
       <c r="Q75">
-        <v>58.68051624327369</v>
+        <v>58.61927851398421</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4072043747473301</v>
+        <v>0.4199439915907751</v>
       </c>
       <c r="T75">
-        <v>2.906243442676085</v>
+        <v>3.008689429776692</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.96169096714429</v>
+        <v>5.881127575696395</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1397836280055074</v>
+        <v>0.1394373736939772</v>
       </c>
       <c r="C76">
-        <v>40.65659705639027</v>
+        <v>39.203965618924</v>
       </c>
       <c r="D76">
-        <v>48.5505970563903</v>
+        <v>48.57896561892401</v>
       </c>
       <c r="E76">
-        <v>73.89400000000002</v>
+        <v>75.37500000000001</v>
       </c>
       <c r="F76">
-        <v>109.594</v>
+        <v>111.075</v>
       </c>
       <c r="G76">
         <v>101.7</v>
@@ -7519,28 +7519,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M76">
-        <v>6.060548200000001</v>
+        <v>6.142447500000001</v>
       </c>
       <c r="N76">
-        <v>29.58230894285715</v>
+        <v>29.50040964285715</v>
       </c>
       <c r="O76">
-        <v>7.463030428872941</v>
+        <v>7.442368858162417</v>
       </c>
       <c r="P76">
-        <v>22.11927851398421</v>
+        <v>22.05804078469473</v>
       </c>
       <c r="Q76">
-        <v>58.61927851398421</v>
+        <v>58.55804078469473</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4199439915907751</v>
+        <v>0.4337027777816957</v>
       </c>
       <c r="T76">
-        <v>3.008689429776692</v>
+        <v>3.119331095845348</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.881127575696395</v>
+        <v>5.802712541353776</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1394373736939772</v>
+        <v>0.139091119382447</v>
       </c>
       <c r="C77">
-        <v>39.203965618924</v>
+        <v>37.75136735286657</v>
       </c>
       <c r="D77">
-        <v>48.57896561892401</v>
+        <v>48.60736735286658</v>
       </c>
       <c r="E77">
-        <v>75.37500000000001</v>
+        <v>76.85600000000001</v>
       </c>
       <c r="F77">
-        <v>111.075</v>
+        <v>112.556</v>
       </c>
       <c r="G77">
         <v>101.7</v>
@@ -7601,28 +7601,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M77">
-        <v>6.142447500000001</v>
+        <v>6.224346800000001</v>
       </c>
       <c r="N77">
-        <v>29.50040964285715</v>
+        <v>29.41851034285715</v>
       </c>
       <c r="O77">
-        <v>7.442368858162417</v>
+        <v>7.421707287451894</v>
       </c>
       <c r="P77">
-        <v>22.05804078469473</v>
+        <v>21.99680305540526</v>
       </c>
       <c r="Q77">
-        <v>58.55804078469473</v>
+        <v>58.49680305540526</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4337027777816957</v>
+        <v>0.4486081294885265</v>
       </c>
       <c r="T77">
-        <v>3.119331095845348</v>
+        <v>3.239192900753059</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.802712541353776</v>
+        <v>5.726361060546489</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.139091119382447</v>
+        <v>0.1387448650709168</v>
       </c>
       <c r="C78">
-        <v>37.75136735286657</v>
+        <v>36.29880231643311</v>
       </c>
       <c r="D78">
-        <v>48.60736735286658</v>
+        <v>48.63580231643312</v>
       </c>
       <c r="E78">
-        <v>76.85600000000001</v>
+        <v>78.33700000000002</v>
       </c>
       <c r="F78">
-        <v>112.556</v>
+        <v>114.037</v>
       </c>
       <c r="G78">
         <v>101.7</v>
@@ -7683,28 +7683,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M78">
-        <v>6.224346800000001</v>
+        <v>6.306246100000001</v>
       </c>
       <c r="N78">
-        <v>29.41851034285715</v>
+        <v>29.33661104285715</v>
       </c>
       <c r="O78">
-        <v>7.421707287451894</v>
+        <v>7.40104571674137</v>
       </c>
       <c r="P78">
-        <v>21.99680305540526</v>
+        <v>21.93556532611578</v>
       </c>
       <c r="Q78">
-        <v>58.49680305540526</v>
+        <v>58.43556532611578</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4486081294885265</v>
+        <v>0.4648095987350816</v>
       </c>
       <c r="T78">
-        <v>3.239192900753059</v>
+        <v>3.369477471304918</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.726361060546489</v>
+        <v>5.651992735084846</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1387448650709168</v>
+        <v>0.1383986107593866</v>
       </c>
       <c r="C79">
-        <v>36.29880231643311</v>
+        <v>34.84627056797505</v>
       </c>
       <c r="D79">
-        <v>48.63580231643312</v>
+        <v>48.66427056797507</v>
       </c>
       <c r="E79">
-        <v>78.33700000000002</v>
+        <v>79.81800000000001</v>
       </c>
       <c r="F79">
-        <v>114.037</v>
+        <v>115.518</v>
       </c>
       <c r="G79">
         <v>101.7</v>
@@ -7765,28 +7765,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M79">
-        <v>6.306246100000001</v>
+        <v>6.388145400000001</v>
       </c>
       <c r="N79">
-        <v>29.33661104285715</v>
+        <v>29.25471174285715</v>
       </c>
       <c r="O79">
-        <v>7.40104571674137</v>
+        <v>7.380384146030847</v>
       </c>
       <c r="P79">
-        <v>21.93556532611578</v>
+        <v>21.8743275968263</v>
       </c>
       <c r="Q79">
-        <v>58.43556532611578</v>
+        <v>58.3743275968263</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4648095987350816</v>
+        <v>0.4824839288222326</v>
       </c>
       <c r="T79">
-        <v>3.369477471304918</v>
+        <v>3.511606093725128</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.651992735084846</v>
+        <v>5.579531289763247</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1383986107593866</v>
+        <v>0.1380523564478564</v>
       </c>
       <c r="C80">
-        <v>34.84627056797505</v>
+        <v>33.39377216598049</v>
       </c>
       <c r="D80">
-        <v>48.66427056797507</v>
+        <v>48.69277216598051</v>
       </c>
       <c r="E80">
-        <v>79.81800000000001</v>
+        <v>81.29900000000002</v>
       </c>
       <c r="F80">
-        <v>115.518</v>
+        <v>116.999</v>
       </c>
       <c r="G80">
         <v>101.7</v>
@@ -7847,28 +7847,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M80">
-        <v>6.388145400000001</v>
+        <v>6.470044700000002</v>
       </c>
       <c r="N80">
-        <v>29.25471174285715</v>
+        <v>29.17281244285715</v>
       </c>
       <c r="O80">
-        <v>7.380384146030847</v>
+        <v>7.359722575320323</v>
       </c>
       <c r="P80">
-        <v>21.8743275968263</v>
+        <v>21.81308986753683</v>
       </c>
       <c r="Q80">
-        <v>58.3743275968263</v>
+        <v>58.31308986753683</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4824839288222326</v>
+        <v>0.5018415284414932</v>
       </c>
       <c r="T80">
-        <v>3.511606093725128</v>
+        <v>3.667270775423453</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.579531289763247</v>
+        <v>5.508904311411812</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1380523564478564</v>
+        <v>0.1377061021363261</v>
       </c>
       <c r="C81">
-        <v>33.39377216598049</v>
+        <v>31.94130716907466</v>
       </c>
       <c r="D81">
-        <v>48.69277216598051</v>
+        <v>48.72130716907469</v>
       </c>
       <c r="E81">
-        <v>81.29900000000002</v>
+        <v>82.78000000000002</v>
       </c>
       <c r="F81">
-        <v>116.999</v>
+        <v>118.48</v>
       </c>
       <c r="G81">
         <v>101.7</v>
@@ -7929,28 +7929,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M81">
-        <v>6.470044700000002</v>
+        <v>6.551944000000002</v>
       </c>
       <c r="N81">
-        <v>29.17281244285715</v>
+        <v>29.09091314285715</v>
       </c>
       <c r="O81">
-        <v>7.359722575320323</v>
+        <v>7.3390610046098</v>
       </c>
       <c r="P81">
-        <v>21.81308986753683</v>
+        <v>21.75185213824735</v>
       </c>
       <c r="Q81">
-        <v>58.31308986753683</v>
+        <v>58.25185213824735</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5018415284414932</v>
+        <v>0.5231348880226799</v>
       </c>
       <c r="T81">
-        <v>3.667270775423453</v>
+        <v>3.83850192529161</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.508904311411812</v>
+        <v>5.440043007519164</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1377061021363261</v>
+        <v>0.1373598478247959</v>
       </c>
       <c r="C82">
-        <v>31.94130716907466</v>
+        <v>30.4888756360203</v>
       </c>
       <c r="D82">
-        <v>48.72130716907469</v>
+        <v>48.74987563602032</v>
       </c>
       <c r="E82">
-        <v>82.78000000000002</v>
+        <v>84.26100000000002</v>
       </c>
       <c r="F82">
-        <v>118.48</v>
+        <v>119.961</v>
       </c>
       <c r="G82">
         <v>101.7</v>
@@ -8011,28 +8011,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M82">
-        <v>6.551944000000002</v>
+        <v>6.633843300000001</v>
       </c>
       <c r="N82">
-        <v>29.09091314285715</v>
+        <v>29.00901384285715</v>
       </c>
       <c r="O82">
-        <v>7.3390610046098</v>
+        <v>7.318399433899276</v>
       </c>
       <c r="P82">
-        <v>21.75185213824735</v>
+        <v>21.69061440895787</v>
       </c>
       <c r="Q82">
-        <v>58.25185213824735</v>
+        <v>58.19061440895787</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5231348880226799</v>
+        <v>0.5466696538755705</v>
       </c>
       <c r="T82">
-        <v>3.83850192529161</v>
+        <v>4.027757406724838</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.440043007519164</v>
+        <v>5.372881982734977</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1373598478247959</v>
+        <v>0.1370135935132657</v>
       </c>
       <c r="C83">
-        <v>30.4888756360203</v>
+        <v>29.03647762571801</v>
       </c>
       <c r="D83">
-        <v>48.74987563602032</v>
+        <v>48.77847762571801</v>
       </c>
       <c r="E83">
-        <v>84.26100000000002</v>
+        <v>85.74200000000002</v>
       </c>
       <c r="F83">
-        <v>119.961</v>
+        <v>121.442</v>
       </c>
       <c r="G83">
         <v>101.7</v>
@@ -8093,28 +8093,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M83">
-        <v>6.633843300000001</v>
+        <v>6.715742600000001</v>
       </c>
       <c r="N83">
-        <v>29.00901384285715</v>
+        <v>28.92711454285715</v>
       </c>
       <c r="O83">
-        <v>7.318399433899276</v>
+        <v>7.297737863188753</v>
       </c>
       <c r="P83">
-        <v>21.69061440895787</v>
+        <v>21.6293766796684</v>
       </c>
       <c r="Q83">
-        <v>58.19061440895787</v>
+        <v>58.1293766796684</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5466696538755705</v>
+        <v>0.5728193937121157</v>
       </c>
       <c r="T83">
-        <v>4.027757406724838</v>
+        <v>4.23804127498398</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.372881982734977</v>
+        <v>5.307359031726014</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1370135935132657</v>
+        <v>0.1366673392017355</v>
       </c>
       <c r="C84">
-        <v>29.03647762571801</v>
+        <v>27.5841131972067</v>
       </c>
       <c r="D84">
-        <v>48.77847762571801</v>
+        <v>48.80711319720673</v>
       </c>
       <c r="E84">
-        <v>85.74200000000002</v>
+        <v>87.22300000000003</v>
       </c>
       <c r="F84">
-        <v>121.442</v>
+        <v>122.923</v>
       </c>
       <c r="G84">
         <v>101.7</v>
@@ -8175,28 +8175,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M84">
-        <v>6.715742600000001</v>
+        <v>6.797641900000002</v>
       </c>
       <c r="N84">
-        <v>28.92711454285715</v>
+        <v>28.84521524285715</v>
       </c>
       <c r="O84">
-        <v>7.297737863188753</v>
+        <v>7.277076292478229</v>
       </c>
       <c r="P84">
-        <v>21.6293766796684</v>
+        <v>21.56813895037892</v>
       </c>
       <c r="Q84">
-        <v>58.1293766796684</v>
+        <v>58.06813895037892</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5728193937121157</v>
+        <v>0.6020455735294307</v>
       </c>
       <c r="T84">
-        <v>4.23804127498398</v>
+        <v>4.473064421861842</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.307359031726014</v>
+        <v>5.243414947006423</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1366673392017355</v>
+        <v>0.1363210848902053</v>
       </c>
       <c r="C85">
-        <v>27.5841131972067</v>
+        <v>26.13178240966405</v>
       </c>
       <c r="D85">
-        <v>48.80711319720673</v>
+        <v>48.83578240966409</v>
       </c>
       <c r="E85">
-        <v>87.22300000000003</v>
+        <v>88.70400000000002</v>
       </c>
       <c r="F85">
-        <v>122.923</v>
+        <v>124.404</v>
       </c>
       <c r="G85">
         <v>101.7</v>
@@ -8257,28 +8257,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M85">
-        <v>6.797641900000002</v>
+        <v>6.879541200000002</v>
       </c>
       <c r="N85">
-        <v>28.84521524285715</v>
+        <v>28.76331594285715</v>
       </c>
       <c r="O85">
-        <v>7.277076292478229</v>
+        <v>7.256414721767706</v>
       </c>
       <c r="P85">
-        <v>21.56813895037892</v>
+        <v>21.50690122108945</v>
       </c>
       <c r="Q85">
-        <v>58.06813895037892</v>
+        <v>58.00690122108945</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6020455735294307</v>
+        <v>0.6349250258239102</v>
       </c>
       <c r="T85">
-        <v>4.473064421861842</v>
+        <v>4.737465462099439</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.243414947006423</v>
+        <v>5.180993340494442</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1363210848902053</v>
+        <v>0.135974830578675</v>
       </c>
       <c r="C86">
-        <v>26.13178240966407</v>
+        <v>24.67948532240689</v>
       </c>
       <c r="D86">
-        <v>48.83578240966409</v>
+        <v>48.86448532240691</v>
       </c>
       <c r="E86">
-        <v>88.70400000000001</v>
+        <v>90.18500000000002</v>
       </c>
       <c r="F86">
-        <v>124.404</v>
+        <v>125.885</v>
       </c>
       <c r="G86">
         <v>101.7</v>
@@ -8339,28 +8339,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M86">
-        <v>6.879541200000001</v>
+        <v>6.961440500000001</v>
       </c>
       <c r="N86">
-        <v>28.76331594285715</v>
+        <v>28.68141664285715</v>
       </c>
       <c r="O86">
-        <v>7.256414721767706</v>
+        <v>7.235753151057183</v>
       </c>
       <c r="P86">
-        <v>21.50690122108945</v>
+        <v>21.44566349179997</v>
       </c>
       <c r="Q86">
-        <v>58.00690122108945</v>
+        <v>57.94566349179997</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6349250258239099</v>
+        <v>0.6721884050909867</v>
       </c>
       <c r="T86">
-        <v>4.737465462099436</v>
+        <v>5.037119974368713</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.180993340494442</v>
+        <v>5.120040477665096</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.135974830578675</v>
+        <v>0.1356285762671448</v>
       </c>
       <c r="C87">
-        <v>24.67948532240689</v>
+        <v>23.22722199489147</v>
       </c>
       <c r="D87">
-        <v>48.86448532240691</v>
+        <v>48.89322199489148</v>
       </c>
       <c r="E87">
-        <v>90.18500000000002</v>
+        <v>91.66600000000001</v>
       </c>
       <c r="F87">
-        <v>125.885</v>
+        <v>127.366</v>
       </c>
       <c r="G87">
         <v>101.7</v>
@@ -8421,28 +8421,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M87">
-        <v>6.961440500000001</v>
+        <v>7.043339800000001</v>
       </c>
       <c r="N87">
-        <v>28.68141664285715</v>
+        <v>28.59951734285715</v>
       </c>
       <c r="O87">
-        <v>7.235753151057183</v>
+        <v>7.215091580346659</v>
       </c>
       <c r="P87">
-        <v>21.44566349179997</v>
+        <v>21.38442576251049</v>
       </c>
       <c r="Q87">
-        <v>57.94566349179997</v>
+        <v>57.88442576251049</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6721884050909867</v>
+        <v>0.7147751242533601</v>
       </c>
       <c r="T87">
-        <v>5.037119974368713</v>
+        <v>5.379582274105028</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.120040477665096</v>
+        <v>5.060505123273642</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1356285762671448</v>
+        <v>0.1352823219556146</v>
       </c>
       <c r="C88">
-        <v>23.22722199489147</v>
+        <v>21.77499248671407</v>
       </c>
       <c r="D88">
-        <v>48.89322199489148</v>
+        <v>48.92199248671408</v>
       </c>
       <c r="E88">
-        <v>91.66600000000001</v>
+        <v>93.14700000000001</v>
       </c>
       <c r="F88">
-        <v>127.366</v>
+        <v>128.847</v>
       </c>
       <c r="G88">
         <v>101.7</v>
@@ -8503,28 +8503,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M88">
-        <v>7.043339800000001</v>
+        <v>7.125239100000001</v>
       </c>
       <c r="N88">
-        <v>28.59951734285715</v>
+        <v>28.51761804285715</v>
       </c>
       <c r="O88">
-        <v>7.215091580346659</v>
+        <v>7.194430009636136</v>
       </c>
       <c r="P88">
-        <v>21.38442576251049</v>
+        <v>21.32318803322102</v>
       </c>
       <c r="Q88">
-        <v>57.88442576251049</v>
+        <v>57.82318803322102</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7147751242533601</v>
+        <v>0.7639136463637909</v>
       </c>
       <c r="T88">
-        <v>5.379582274105028</v>
+        <v>5.774731081493083</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.060505123273642</v>
+        <v>5.002338397718773</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1352823219556146</v>
+        <v>0.1349360676440844</v>
       </c>
       <c r="C89">
-        <v>21.77499248671407</v>
+        <v>20.32279685761128</v>
       </c>
       <c r="D89">
-        <v>48.92199248671408</v>
+        <v>48.95079685761132</v>
       </c>
       <c r="E89">
-        <v>93.14700000000001</v>
+        <v>94.62800000000003</v>
       </c>
       <c r="F89">
-        <v>128.847</v>
+        <v>130.328</v>
       </c>
       <c r="G89">
         <v>101.7</v>
@@ -8585,28 +8585,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M89">
-        <v>7.125239100000001</v>
+        <v>7.207138400000002</v>
       </c>
       <c r="N89">
-        <v>28.51761804285715</v>
+        <v>28.43571874285715</v>
       </c>
       <c r="O89">
-        <v>7.194430009636136</v>
+        <v>7.173768438925612</v>
       </c>
       <c r="P89">
-        <v>21.32318803322102</v>
+        <v>21.26195030393154</v>
       </c>
       <c r="Q89">
-        <v>57.82318803322102</v>
+        <v>57.76195030393154</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7639136463637909</v>
+        <v>0.8212419221592936</v>
       </c>
       <c r="T89">
-        <v>5.774731081493083</v>
+        <v>6.235738023445816</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.002338397718773</v>
+        <v>4.94549364319924</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1349360676440844</v>
+        <v>0.1345898133325542</v>
       </c>
       <c r="C90">
-        <v>20.32279685761128</v>
+        <v>18.87063516746053</v>
       </c>
       <c r="D90">
-        <v>48.95079685761132</v>
+        <v>48.97963516746056</v>
       </c>
       <c r="E90">
-        <v>94.62800000000003</v>
+        <v>96.10900000000002</v>
       </c>
       <c r="F90">
-        <v>130.328</v>
+        <v>131.809</v>
       </c>
       <c r="G90">
         <v>101.7</v>
@@ -8667,28 +8667,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M90">
-        <v>7.207138400000002</v>
+        <v>7.289037700000002</v>
       </c>
       <c r="N90">
-        <v>28.43571874285715</v>
+        <v>28.35381944285715</v>
       </c>
       <c r="O90">
-        <v>7.173768438925612</v>
+        <v>7.153106868215088</v>
       </c>
       <c r="P90">
-        <v>21.26195030393154</v>
+        <v>21.20071257464206</v>
       </c>
       <c r="Q90">
-        <v>57.76195030393154</v>
+        <v>57.70071257464206</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8212419221592936</v>
+        <v>0.8889935208267059</v>
       </c>
       <c r="T90">
-        <v>6.235738023445816</v>
+        <v>6.780564409389954</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.94549364319924</v>
+        <v>4.889926298893631</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1345898133325542</v>
+        <v>0.134243559021024</v>
       </c>
       <c r="C91">
-        <v>18.87063516746053</v>
+        <v>17.41850747628038</v>
       </c>
       <c r="D91">
-        <v>48.97963516746056</v>
+        <v>49.0085074762804</v>
       </c>
       <c r="E91">
-        <v>96.10900000000002</v>
+        <v>97.59000000000002</v>
       </c>
       <c r="F91">
-        <v>131.809</v>
+        <v>133.29</v>
       </c>
       <c r="G91">
         <v>101.7</v>
@@ -8749,28 +8749,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M91">
-        <v>7.289037700000002</v>
+        <v>7.370937000000001</v>
       </c>
       <c r="N91">
-        <v>28.35381944285715</v>
+        <v>28.27192014285715</v>
       </c>
       <c r="O91">
-        <v>7.153106868215088</v>
+        <v>7.132445297504566</v>
       </c>
       <c r="P91">
-        <v>21.20071257464206</v>
+        <v>21.13947484535259</v>
       </c>
       <c r="Q91">
-        <v>57.70071257464206</v>
+        <v>57.63947484535259</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8889935208267059</v>
+        <v>0.9702954392276006</v>
       </c>
       <c r="T91">
-        <v>6.780564409389954</v>
+        <v>7.434356072522919</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.889926298893631</v>
+        <v>4.83559378446148</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.134243559021024</v>
+        <v>0.1338973047094938</v>
       </c>
       <c r="C92">
-        <v>17.41850747628038</v>
+        <v>15.966413844231</v>
       </c>
       <c r="D92">
-        <v>49.0085074762804</v>
+        <v>49.037413844231</v>
       </c>
       <c r="E92">
-        <v>97.59000000000002</v>
+        <v>99.07100000000001</v>
       </c>
       <c r="F92">
-        <v>133.29</v>
+        <v>134.771</v>
       </c>
       <c r="G92">
         <v>101.7</v>
@@ -8831,28 +8831,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M92">
-        <v>7.370937000000001</v>
+        <v>7.452836300000001</v>
       </c>
       <c r="N92">
-        <v>28.27192014285715</v>
+        <v>28.19002084285715</v>
       </c>
       <c r="O92">
-        <v>7.132445297504566</v>
+        <v>7.111783726794042</v>
       </c>
       <c r="P92">
-        <v>21.13947484535259</v>
+        <v>21.07823711606311</v>
       </c>
       <c r="Q92">
-        <v>57.63947484535259</v>
+        <v>57.57823711606311</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9702954392276006</v>
+        <v>1.069664450606472</v>
       </c>
       <c r="T92">
-        <v>7.434356072522919</v>
+        <v>8.233434771907657</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.83559378446148</v>
+        <v>4.782455391225639</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1338973047094938</v>
+        <v>0.1335510503979636</v>
       </c>
       <c r="C93">
-        <v>15.966413844231</v>
+        <v>14.51435433161453</v>
       </c>
       <c r="D93">
-        <v>49.037413844231</v>
+        <v>49.06635433161456</v>
       </c>
       <c r="E93">
-        <v>99.07100000000001</v>
+        <v>100.552</v>
       </c>
       <c r="F93">
-        <v>134.771</v>
+        <v>136.252</v>
       </c>
       <c r="G93">
         <v>101.7</v>
@@ -8913,28 +8913,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M93">
-        <v>7.452836300000001</v>
+        <v>7.534735600000002</v>
       </c>
       <c r="N93">
-        <v>28.19002084285715</v>
+        <v>28.10812154285715</v>
       </c>
       <c r="O93">
-        <v>7.111783726794042</v>
+        <v>7.091122156083518</v>
       </c>
       <c r="P93">
-        <v>21.07823711606311</v>
+        <v>21.01699938677363</v>
       </c>
       <c r="Q93">
-        <v>57.57823711606311</v>
+        <v>57.51699938677363</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.069664450606472</v>
+        <v>1.193875714830062</v>
       </c>
       <c r="T93">
-        <v>8.233434771907657</v>
+        <v>9.232283146138577</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.782455391225639</v>
+        <v>4.730472180451447</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1335510503979636</v>
+        <v>0.1332047960864333</v>
       </c>
       <c r="C94">
-        <v>14.51435433161453</v>
+        <v>13.06232899887567</v>
       </c>
       <c r="D94">
-        <v>49.06635433161456</v>
+        <v>49.0953289988757</v>
       </c>
       <c r="E94">
-        <v>100.552</v>
+        <v>102.033</v>
       </c>
       <c r="F94">
-        <v>136.252</v>
+        <v>137.733</v>
       </c>
       <c r="G94">
         <v>101.7</v>
@@ -8995,28 +8995,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M94">
-        <v>7.534735600000002</v>
+        <v>7.616634900000002</v>
       </c>
       <c r="N94">
-        <v>28.10812154285715</v>
+        <v>28.02622224285715</v>
       </c>
       <c r="O94">
-        <v>7.091122156083518</v>
+        <v>7.070460585372995</v>
       </c>
       <c r="P94">
-        <v>21.01699938677363</v>
+        <v>20.95576165748416</v>
       </c>
       <c r="Q94">
-        <v>57.51699938677363</v>
+        <v>57.45576165748416</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.193875714830062</v>
+        <v>1.353575911688962</v>
       </c>
       <c r="T94">
-        <v>9.232283146138577</v>
+        <v>10.51651677014976</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.730472180451447</v>
+        <v>4.679606888188529</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1332047960864333</v>
+        <v>0.1328585417749031</v>
       </c>
       <c r="C95">
-        <v>13.06232899887567</v>
+        <v>11.6103379066019</v>
       </c>
       <c r="D95">
-        <v>49.0953289988757</v>
+        <v>49.12433790660193</v>
       </c>
       <c r="E95">
-        <v>102.033</v>
+        <v>103.514</v>
       </c>
       <c r="F95">
-        <v>137.733</v>
+        <v>139.214</v>
       </c>
       <c r="G95">
         <v>101.7</v>
@@ -9077,28 +9077,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M95">
-        <v>7.616634900000002</v>
+        <v>7.698534200000002</v>
       </c>
       <c r="N95">
-        <v>28.02622224285715</v>
+        <v>27.94432294285715</v>
       </c>
       <c r="O95">
-        <v>7.070460585372995</v>
+        <v>7.049799014662471</v>
       </c>
       <c r="P95">
-        <v>20.95576165748416</v>
+        <v>20.89452392819468</v>
       </c>
       <c r="Q95">
-        <v>57.45576165748416</v>
+        <v>57.39452392819468</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.353575911688962</v>
+        <v>1.56650950750083</v>
       </c>
       <c r="T95">
-        <v>10.51651677014976</v>
+        <v>12.22882826883134</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.679606888188529</v>
+        <v>4.629823836186523</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1328585417749031</v>
+        <v>0.1325122874633729</v>
       </c>
       <c r="C96">
-        <v>11.6103379066019</v>
+        <v>10.15838111552398</v>
       </c>
       <c r="D96">
-        <v>49.12433790660193</v>
+        <v>49.15338111552399</v>
       </c>
       <c r="E96">
-        <v>103.514</v>
+        <v>104.995</v>
       </c>
       <c r="F96">
-        <v>139.214</v>
+        <v>140.695</v>
       </c>
       <c r="G96">
         <v>101.7</v>
@@ -9159,28 +9159,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M96">
-        <v>7.698534200000002</v>
+        <v>7.780433500000002</v>
       </c>
       <c r="N96">
-        <v>27.94432294285715</v>
+        <v>27.86242364285715</v>
       </c>
       <c r="O96">
-        <v>7.049799014662471</v>
+        <v>7.029137443951949</v>
       </c>
       <c r="P96">
-        <v>20.89452392819468</v>
+        <v>20.8332861989052</v>
       </c>
       <c r="Q96">
-        <v>57.39452392819468</v>
+        <v>57.3332861989052</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.56650950750083</v>
+        <v>1.864616541637445</v>
       </c>
       <c r="T96">
-        <v>12.22882826883134</v>
+        <v>14.62606436698555</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.629823836186523</v>
+        <v>4.581088848437192</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1325122874633729</v>
+        <v>0.1321660331518427</v>
       </c>
       <c r="C97">
-        <v>10.15838111552398</v>
+        <v>8.706458686516328</v>
       </c>
       <c r="D97">
-        <v>49.15338111552399</v>
+        <v>49.18245868651638</v>
       </c>
       <c r="E97">
-        <v>104.995</v>
+        <v>106.476</v>
       </c>
       <c r="F97">
-        <v>140.695</v>
+        <v>142.176</v>
       </c>
       <c r="G97">
         <v>101.7</v>
@@ -9241,28 +9241,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M97">
-        <v>7.780433500000002</v>
+        <v>7.862332800000003</v>
       </c>
       <c r="N97">
-        <v>27.86242364285715</v>
+        <v>27.78052434285715</v>
       </c>
       <c r="O97">
-        <v>7.029137443951949</v>
+        <v>7.008475873241424</v>
       </c>
       <c r="P97">
-        <v>20.8332861989052</v>
+        <v>20.77204846961573</v>
       </c>
       <c r="Q97">
-        <v>57.3332861989052</v>
+        <v>57.27204846961573</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.864616541637445</v>
+        <v>2.311777092842367</v>
       </c>
       <c r="T97">
-        <v>14.62606436698555</v>
+        <v>18.22191851421688</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.581088848437192</v>
+        <v>4.533369172932637</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1321660331518427</v>
+        <v>0.1336329993870935</v>
       </c>
       <c r="C98">
-        <v>8.706458686516356</v>
+        <v>7.10250181925872</v>
       </c>
       <c r="D98">
-        <v>49.18245868651638</v>
+        <v>49.05950181925872</v>
       </c>
       <c r="E98">
-        <v>106.476</v>
+        <v>107.957</v>
       </c>
       <c r="F98">
-        <v>142.176</v>
+        <v>143.657</v>
       </c>
       <c r="G98">
         <v>101.7</v>
@@ -9323,45 +9323,45 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M98">
-        <v>7.862332800000001</v>
+        <v>8.303374600000001</v>
       </c>
       <c r="N98">
-        <v>27.78052434285715</v>
+        <v>27.33948254285715</v>
       </c>
       <c r="O98">
-        <v>7.008475873241425</v>
+        <v>6.897209765509166</v>
       </c>
       <c r="P98">
-        <v>20.77204846961573</v>
+        <v>20.44227277734798</v>
       </c>
       <c r="Q98">
-        <v>57.27204846961573</v>
+        <v>56.94227277734798</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.311777092842361</v>
+        <v>3.057044678183895</v>
       </c>
       <c r="T98">
-        <v>18.22191851421683</v>
+        <v>24.21500875960234</v>
       </c>
       <c r="U98">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V98">
         <v>0.2522801868944358</v>
       </c>
       <c r="W98">
-        <v>0.0413489056647377</v>
+        <v>0.04321820519750161</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y98">
-        <v>4.533369172932638</v>
+        <v>4.29257486984354</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1336329993870935</v>
+        <v>0.1333054380708909</v>
       </c>
       <c r="C99">
-        <v>7.10250181925872</v>
+        <v>5.648903719570853</v>
       </c>
       <c r="D99">
-        <v>49.05950181925872</v>
+        <v>49.08690371957088</v>
       </c>
       <c r="E99">
-        <v>107.957</v>
+        <v>109.438</v>
       </c>
       <c r="F99">
-        <v>143.657</v>
+        <v>145.138</v>
       </c>
       <c r="G99">
         <v>101.7</v>
@@ -9405,28 +9405,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M99">
-        <v>8.303374600000001</v>
+        <v>8.388976400000002</v>
       </c>
       <c r="N99">
-        <v>27.33948254285715</v>
+        <v>27.25388074285715</v>
       </c>
       <c r="O99">
-        <v>6.897209765509166</v>
+        <v>6.875614127406665</v>
       </c>
       <c r="P99">
-        <v>20.44227277734798</v>
+        <v>20.37826661545049</v>
       </c>
       <c r="Q99">
-        <v>56.94227277734798</v>
+        <v>56.87826661545049</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.057044678183895</v>
+        <v>4.547579848866962</v>
       </c>
       <c r="T99">
-        <v>24.21500875960234</v>
+        <v>36.20118925037335</v>
       </c>
       <c r="U99">
         <v>0.0578</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.29257486984354</v>
+        <v>4.24877308545738</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1333054380708909</v>
+        <v>0.1329778767546883</v>
       </c>
       <c r="C100">
-        <v>5.648903719570853</v>
+        <v>4.195336247334922</v>
       </c>
       <c r="D100">
-        <v>49.08690371957088</v>
+        <v>49.11433624733493</v>
       </c>
       <c r="E100">
-        <v>109.438</v>
+        <v>110.919</v>
       </c>
       <c r="F100">
-        <v>145.138</v>
+        <v>146.619</v>
       </c>
       <c r="G100">
         <v>101.7</v>
@@ -9487,28 +9487,28 @@
         <v>35.64285714285715</v>
       </c>
       <c r="M100">
-        <v>8.388976400000002</v>
+        <v>8.474578200000002</v>
       </c>
       <c r="N100">
-        <v>27.25388074285715</v>
+        <v>27.16827894285715</v>
       </c>
       <c r="O100">
-        <v>6.875614127406665</v>
+        <v>6.854018489304165</v>
       </c>
       <c r="P100">
-        <v>20.37826661545049</v>
+        <v>20.31426045355298</v>
       </c>
       <c r="Q100">
-        <v>56.87826661545049</v>
+        <v>56.81426045355298</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.547579848866962</v>
+        <v>9.019185360916165</v>
       </c>
       <c r="T100">
-        <v>36.20118925037335</v>
+        <v>72.1597307226864</v>
       </c>
       <c r="U100">
         <v>0.0578</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.24877308545738</v>
+        <v>4.205856185604276</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1329778767546883</v>
-      </c>
-      <c r="C101">
-        <v>4.195336247334922</v>
-      </c>
-      <c r="D101">
-        <v>49.11433624733493</v>
-      </c>
-      <c r="E101">
-        <v>110.919</v>
-      </c>
-      <c r="F101">
-        <v>146.619</v>
-      </c>
-      <c r="G101">
-        <v>101.7</v>
-      </c>
-      <c r="H101">
-        <v>112.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>72.14285714285715</v>
-      </c>
-      <c r="K101">
-        <v>36.5</v>
-      </c>
-      <c r="L101">
-        <v>35.64285714285715</v>
-      </c>
-      <c r="M101">
-        <v>8.474578200000002</v>
-      </c>
-      <c r="N101">
-        <v>27.16827894285715</v>
-      </c>
-      <c r="O101">
-        <v>6.854018489304165</v>
-      </c>
-      <c r="P101">
-        <v>20.31426045355298</v>
-      </c>
-      <c r="Q101">
-        <v>56.81426045355298</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.019185360916165</v>
-      </c>
-      <c r="T101">
-        <v>72.1597307226864</v>
-      </c>
-      <c r="U101">
-        <v>0.0578</v>
-      </c>
-      <c r="V101">
-        <v>0.2522801868944358</v>
-      </c>
-      <c r="W101">
-        <v>0.04321820519750161</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Baa2/BBB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.205856185604276</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
